--- a/ILLIA/Junio/ILLIA-JUNIO.xlsx
+++ b/ILLIA/Junio/ILLIA-JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AE2241-FB2F-4361-9431-3F645C0D18C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661A9F4F-AF68-438B-8606-9FFDB9F1E0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Copia de PRORRATEO'!$A$1:$Q$46</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$140</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$141</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="186">
   <si>
     <t>TELEFONO: 11 5320-2676</t>
   </si>
@@ -102,9 +102,6 @@
     <t>Mercantil Andina - Poliza nro 001175538</t>
   </si>
   <si>
-    <t>Debito 21/05</t>
-  </si>
-  <si>
     <t>TOTAL IMPUESTO</t>
   </si>
   <si>
@@ -114,15 +111,9 @@
     <t>ARCA931 VEP</t>
   </si>
   <si>
-    <t>Transf 13/05</t>
-  </si>
-  <si>
     <t>Suther</t>
   </si>
   <si>
-    <t>Debito 12/05</t>
-  </si>
-  <si>
     <t>Fatheryh</t>
   </si>
   <si>
@@ -135,18 +126,12 @@
     <t>ABONOS Y SERVICIOS</t>
   </si>
   <si>
-    <t>Transf 07/05</t>
-  </si>
-  <si>
     <t>Servicio Fumigacion - Nancy</t>
   </si>
   <si>
     <t>TELECOM - 99336146</t>
   </si>
   <si>
-    <t xml:space="preserve">Debito </t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
@@ -168,9 +153,6 @@
     <t>MANTENIMIENTO DE CUENTA BANCARIA</t>
   </si>
   <si>
-    <t>PREVISION ORDINARIA - LIMPIEZA DE TANQUES Y ARREGLOS DE TECHO</t>
-  </si>
-  <si>
     <t xml:space="preserve">TOTAL ORDINARIOS </t>
   </si>
   <si>
@@ -195,9 +177,6 @@
     <t>GASTOS EXTRAORDINARIOS CON PREVISION:</t>
   </si>
   <si>
-    <t>LAS EXPENSAS SON CERRADAS EL DIA 29/05 A LAS 12 DEL MEDIODIA ENTENDIENDO QUE UNA GRAN PARTE DE LOS VECINOS NO ABONO LAS EXPENSAS</t>
-  </si>
-  <si>
     <t>RESUMEN</t>
   </si>
   <si>
@@ -486,9 +465,6 @@
     <t>Pablo Moyano o laura</t>
   </si>
   <si>
-    <t>PABLO MAOYANO PAGO EL 31/05 PERO LA HABIAMOS CERRADO ANTES</t>
-  </si>
-  <si>
     <t>15º</t>
   </si>
   <si>
@@ -552,9 +528,6 @@
     <t>PERÍODO: JUNIO</t>
   </si>
   <si>
-    <t>Sueldo Ana encargada JUNIO</t>
-  </si>
-  <si>
     <t>Claudio Sosa Periodo JUNIO</t>
   </si>
   <si>
@@ -564,29 +537,63 @@
     <t>Ascensores ADS - Mantenimiento de ascensor (Período JUNIO)</t>
   </si>
   <si>
-    <t>AYSA - Cuota plan de pagos - Mes de JUNIO</t>
-  </si>
-  <si>
     <t>AYSA - Mes de JUNIO</t>
   </si>
   <si>
     <t>GASTOS BANCARIOS JUNIO Y JUNIO</t>
   </si>
   <si>
-    <t>Mes de MAYO - Se debe JUNIO</t>
-  </si>
-  <si>
-    <t>Mes de MAYO y JUNIO</t>
-  </si>
-  <si>
     <t>Transf 09/06</t>
+  </si>
+  <si>
+    <t>Sueldo Ana encargada JUNIO y SAC</t>
+  </si>
+  <si>
+    <t>MAYO Y JUNIO</t>
+  </si>
+  <si>
+    <t>JUNIO</t>
+  </si>
+  <si>
+    <t>Debito 21/05/</t>
+  </si>
+  <si>
+    <t>Transf 23/06</t>
+  </si>
+  <si>
+    <t>Debito 12/06</t>
+  </si>
+  <si>
+    <t>Sindicato plan de pago - cuota 2 seracarh</t>
+  </si>
+  <si>
+    <t>Debito 04/06</t>
+  </si>
+  <si>
+    <t>Transf 11/06</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA</t>
+  </si>
+  <si>
+    <t>Punitorios mal cobrados</t>
+  </si>
+  <si>
+    <t>Transf 18/06</t>
+  </si>
+  <si>
+    <t>Servisur reemplazo lamparas dicroicas, fotocelulas y plafones</t>
+  </si>
+  <si>
+    <t>Casa ruan - compra de materiales</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
@@ -814,13 +821,14 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFEE0000"/>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -920,13 +928,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFEE0000"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE0000"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1431,7 +1445,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="29"/>
   </cellStyleXfs>
-  <cellXfs count="263">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1691,25 +1705,6 @@
     <xf numFmtId="170" fontId="18" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="19" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="23" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="18" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="18" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="31" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1731,12 +1726,8 @@
     <xf numFmtId="165" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="7" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="28" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="28" fillId="12" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="28" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1757,16 +1748,30 @@
     <xf numFmtId="165" fontId="7" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
@@ -1779,46 +1784,19 @@
     <xf numFmtId="165" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1826,8 +1804,12 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1836,23 +1818,51 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="33" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="21" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="28" fillId="19" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="19" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="18" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="18" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2069,7 +2079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1006"/>
+  <dimension ref="A1:Z1007"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.42578125" customWidth="1"/>
@@ -2108,11 +2118,11 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
-      <c r="B3" s="222" t="s">
+      <c r="B3" s="219" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="223"/>
-      <c r="D3" s="223"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="209"/>
       <c r="E3" s="9"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -2120,9 +2130,9 @@
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
-      <c r="B4" s="224"/>
-      <c r="C4" s="224"/>
-      <c r="D4" s="224"/>
+      <c r="B4" s="211"/>
+      <c r="C4" s="211"/>
+      <c r="D4" s="211"/>
       <c r="E4" s="9"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -2147,7 +2157,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15" t="s">
@@ -2160,13 +2170,13 @@
       <c r="I6" s="156"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="238" t="s">
+      <c r="A7" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="224"/>
-      <c r="C7" s="224"/>
-      <c r="D7" s="224"/>
-      <c r="E7" s="239"/>
+      <c r="B7" s="211"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="212"/>
       <c r="F7" s="17"/>
       <c r="G7" s="157"/>
       <c r="H7" s="157"/>
@@ -2179,10 +2189,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="230" t="s">
+      <c r="B9" s="223" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="223"/>
+      <c r="C9" s="209"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -2191,8 +2201,8 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="223"/>
-      <c r="C10" s="223"/>
+      <c r="B10" s="209"/>
+      <c r="C10" s="209"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -2201,8 +2211,8 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="223"/>
-      <c r="C11" s="223"/>
+      <c r="B11" s="209"/>
+      <c r="C11" s="209"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -2221,43 +2231,43 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="240" t="s">
+      <c r="A14" s="213" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="223"/>
-      <c r="C14" s="223"/>
-      <c r="D14" s="223"/>
-      <c r="E14" s="223"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
+      <c r="E14" s="209"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="223"/>
-      <c r="B15" s="223"/>
-      <c r="C15" s="223"/>
-      <c r="D15" s="223"/>
-      <c r="E15" s="223"/>
+      <c r="A15" s="209"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="209"/>
+      <c r="E15" s="209"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="223"/>
-      <c r="B16" s="223"/>
-      <c r="C16" s="223"/>
-      <c r="D16" s="223"/>
-      <c r="E16" s="223"/>
+      <c r="A16" s="209"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="223"/>
-      <c r="B17" s="223"/>
-      <c r="C17" s="223"/>
-      <c r="D17" s="223"/>
-      <c r="E17" s="223"/>
+      <c r="A17" s="209"/>
+      <c r="B17" s="209"/>
+      <c r="C17" s="209"/>
+      <c r="D17" s="209"/>
+      <c r="E17" s="209"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
@@ -2300,12 +2310,12 @@
     </row>
     <row r="23" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="190">
-        <v>571966.6</v>
+      <c r="D23" s="179">
+        <v>880374.6</v>
       </c>
       <c r="E23" s="25"/>
     </row>
@@ -2313,7 +2323,7 @@
       <c r="A24" s="25"/>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
-      <c r="D24" s="190"/>
+      <c r="D24" s="179"/>
       <c r="E24" s="25"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -2341,7 +2351,7 @@
       <c r="A25" s="25"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
-      <c r="D25" s="190"/>
+      <c r="D25" s="179"/>
       <c r="E25" s="25"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -2371,8 +2381,8 @@
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
-      <c r="D26" s="190">
-        <v>-141561.75</v>
+      <c r="D26" s="179">
+        <v>-217892.73</v>
       </c>
       <c r="E26" s="25"/>
     </row>
@@ -2382,8 +2392,8 @@
       </c>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
-      <c r="D27" s="190">
-        <v>0.15</v>
+      <c r="D27" s="179">
+        <v>0.13</v>
       </c>
       <c r="E27" s="25"/>
       <c r="F27" s="4"/>
@@ -2414,9 +2424,9 @@
       </c>
       <c r="B28" s="26"/>
       <c r="C28" s="26"/>
-      <c r="D28" s="191">
+      <c r="D28" s="180">
         <f>SUM(D23:D27)</f>
-        <v>430405</v>
+        <v>662482</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="4"/>
@@ -2443,18 +2453,18 @@
     </row>
     <row r="29" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
-      <c r="D29" s="190"/>
+      <c r="D29" s="179"/>
       <c r="E29" s="25"/>
     </row>
     <row r="30" spans="1:26" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="28"/>
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
-      <c r="D30" s="190"/>
+      <c r="D30" s="179"/>
       <c r="E30" s="25"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -2482,14 +2492,14 @@
       <c r="A31" s="25"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
-      <c r="D31" s="190"/>
+      <c r="D31" s="179"/>
       <c r="E31" s="25"/>
     </row>
     <row r="32" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="25"/>
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
-      <c r="D32" s="192"/>
+      <c r="D32" s="181"/>
       <c r="E32" s="25"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
@@ -2517,7 +2527,7 @@
       <c r="A33" s="25"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
-      <c r="D33" s="192"/>
+      <c r="D33" s="181"/>
       <c r="E33" s="25"/>
       <c r="F33" s="4"/>
     </row>
@@ -2527,7 +2537,7 @@
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
-      <c r="D34" s="192"/>
+      <c r="D34" s="181"/>
       <c r="E34" s="25"/>
       <c r="F34" s="4"/>
     </row>
@@ -2537,7 +2547,7 @@
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
-      <c r="D35" s="192"/>
+      <c r="D35" s="181"/>
       <c r="E35" s="25"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -2565,7 +2575,7 @@
       <c r="A36" s="25"/>
       <c r="B36" s="25"/>
       <c r="C36" s="25"/>
-      <c r="D36" s="192"/>
+      <c r="D36" s="181"/>
       <c r="E36" s="25"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
@@ -2595,7 +2605,7 @@
       </c>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
-      <c r="D37" s="193">
+      <c r="D37" s="182">
         <f>SUM(D29:D36)</f>
         <v>0</v>
       </c>
@@ -2628,10 +2638,10 @@
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>
-      <c r="D38" s="194"/>
+      <c r="D38" s="183"/>
       <c r="E38" s="30">
         <f>D28+D37</f>
-        <v>430405</v>
+        <v>662482</v>
       </c>
       <c r="F38" s="31"/>
     </row>
@@ -2641,7 +2651,7 @@
       </c>
       <c r="B39" s="24"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="195"/>
+      <c r="D39" s="184"/>
       <c r="E39" s="32"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
@@ -2669,12 +2679,13 @@
       <c r="A40" s="140" t="s">
         <v>18</v>
       </c>
-      <c r="B40" s="260" t="s">
-        <v>181</v>
+      <c r="B40" s="243" t="s">
+        <v>173</v>
       </c>
       <c r="C40" s="25"/>
-      <c r="D40" s="259">
-        <v>28000</v>
+      <c r="D40" s="249">
+        <f>2*28000</f>
+        <v>56000</v>
       </c>
       <c r="E40" s="34"/>
       <c r="F40" s="4"/>
@@ -2703,13 +2714,13 @@
       <c r="A41" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B41" s="260" t="s">
-        <v>182</v>
+      <c r="B41" s="243" t="s">
+        <v>174</v>
       </c>
       <c r="C41" s="25"/>
-      <c r="D41" s="261">
-        <f>2*114000</f>
-        <v>228000</v>
+      <c r="D41" s="179">
+        <f>114000</f>
+        <v>114000</v>
       </c>
       <c r="E41" s="34"/>
       <c r="F41" s="4"/>
@@ -2742,10 +2753,10 @@
       </c>
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
-      <c r="D42" s="196"/>
+      <c r="D42" s="185"/>
       <c r="E42" s="35">
         <f>SUM(D40:D41)</f>
-        <v>256000</v>
+        <v>170000</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -2775,44 +2786,44 @@
       </c>
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
-      <c r="D43" s="197"/>
+      <c r="D43" s="186"/>
       <c r="E43" s="36"/>
       <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="235" t="s">
+      <c r="A44" s="227" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="226"/>
+      <c r="B44" s="215"/>
       <c r="C44" s="37"/>
-      <c r="D44" s="199">
-        <v>50274.73</v>
+      <c r="D44" s="188">
+        <v>56041.08</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="29"/>
-      <c r="D45" s="196"/>
+      <c r="D45" s="185"/>
       <c r="E45" s="40">
         <f>SUM(D44:D44)</f>
-        <v>50274.73</v>
+        <v>56041.08</v>
       </c>
       <c r="F45" s="4"/>
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B46" s="41"/>
       <c r="C46" s="41"/>
-      <c r="D46" s="200"/>
+      <c r="D46" s="189"/>
       <c r="E46" s="42"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
@@ -2840,157 +2851,137 @@
       <c r="A47" s="25"/>
       <c r="B47" s="25"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="201"/>
+      <c r="D47" s="190"/>
       <c r="E47" s="45"/>
       <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B48" s="25"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="218">
-        <v>335906.93</v>
+      <c r="D48" s="205">
+        <v>318799.93</v>
       </c>
       <c r="E48" s="165" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="F48" s="4"/>
     </row>
-    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" s="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="B49" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C49" s="25"/>
-      <c r="D49" s="201">
+        <v>178</v>
+      </c>
+      <c r="B49" s="25"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="205">
+        <v>70000</v>
+      </c>
+      <c r="E49" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="F49" s="244"/>
+    </row>
+    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" s="25"/>
+      <c r="D50" s="190">
         <v>25738.5</v>
       </c>
-      <c r="E49" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
-      <c r="W49" s="4"/>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
-      <c r="Z49" s="4"/>
-    </row>
-    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="25" t="str">
-        <f>A49</f>
-        <v>Sindicatos mes de JUNIO</v>
-      </c>
-      <c r="B50" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="25"/>
-      <c r="D50" s="199">
-        <v>61177.83</v>
-      </c>
-      <c r="E50" s="46" t="str">
-        <f>E49</f>
-        <v>Debito 12/05</v>
+      <c r="E50" s="46" t="s">
+        <v>177</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4"/>
+      <c r="V50" s="4"/>
+      <c r="W50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
     </row>
     <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="160" t="str">
+      <c r="A51" s="25" t="str">
         <f>A50</f>
         <v>Sindicatos mes de JUNIO</v>
       </c>
-      <c r="B51" s="160" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="160"/>
-      <c r="D51" s="219">
-        <v>2859.83</v>
-      </c>
-      <c r="E51" s="47" t="str">
+      <c r="B51" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" s="25"/>
+      <c r="D51" s="188">
+        <v>61177.83</v>
+      </c>
+      <c r="E51" s="46" t="str">
         <f>E50</f>
-        <v>Debito 12/05</v>
+        <v>Debito 12/06</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="161" t="s">
-        <v>33</v>
-      </c>
-      <c r="B52" s="162"/>
-      <c r="C52" s="162"/>
-      <c r="D52" s="202"/>
-      <c r="E52" s="40">
-        <f>SUM(D47:D51)</f>
-        <v>425683.09</v>
+    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="160" t="str">
+        <f>A51</f>
+        <v>Sindicatos mes de JUNIO</v>
+      </c>
+      <c r="B52" s="160" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="160"/>
+      <c r="D52" s="206">
+        <v>2859.83</v>
+      </c>
+      <c r="E52" s="47" t="str">
+        <f>E51</f>
+        <v>Debito 12/06</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B53" s="41"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="200"/>
-      <c r="E53" s="42"/>
+    <row r="53" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="161" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" s="162"/>
+      <c r="C53" s="162"/>
+      <c r="D53" s="191"/>
+      <c r="E53" s="40">
+        <f>SUM(D47:D52)</f>
+        <v>478576.09</v>
+      </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-    </row>
-    <row r="54" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="234" t="s">
-        <v>177</v>
-      </c>
-      <c r="B54" s="226"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="257">
-        <v>94000</v>
-      </c>
-      <c r="E54" s="163" t="s">
-        <v>183</v>
-      </c>
+    </row>
+    <row r="54" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" s="41"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="189"/>
+      <c r="E54" s="42"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -3013,17 +3004,17 @@
       <c r="Y54" s="4"/>
       <c r="Z54" s="4"/>
     </row>
-    <row r="55" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="172" t="s">
-        <v>36</v>
-      </c>
-      <c r="B55" s="173"/>
+    <row r="55" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="226" t="s">
+        <v>168</v>
+      </c>
+      <c r="B55" s="215"/>
       <c r="C55" s="25"/>
-      <c r="D55" s="203">
-        <v>30000</v>
+      <c r="D55" s="192">
+        <v>94000</v>
       </c>
       <c r="E55" s="163" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
@@ -3047,168 +3038,198 @@
       <c r="Y55" s="4"/>
       <c r="Z55" s="4"/>
     </row>
-    <row r="56" spans="1:26" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="139" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="138"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="262">
+    <row r="56" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="172" t="s">
+        <v>32</v>
+      </c>
+      <c r="B56" s="173"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="192"/>
+      <c r="E56" s="163"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+    </row>
+    <row r="57" spans="1:26" s="245" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="248" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57" s="173"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="192">
+        <v>157000</v>
+      </c>
+      <c r="E57" s="150" t="s">
+        <v>183</v>
+      </c>
+      <c r="F57" s="244"/>
+      <c r="G57" s="244"/>
+      <c r="H57" s="244"/>
+      <c r="I57" s="244"/>
+      <c r="J57" s="244"/>
+      <c r="K57" s="244"/>
+      <c r="L57" s="244"/>
+      <c r="M57" s="244"/>
+      <c r="N57" s="244"/>
+      <c r="O57" s="244"/>
+      <c r="P57" s="244"/>
+      <c r="Q57" s="244"/>
+      <c r="R57" s="244"/>
+      <c r="S57" s="244"/>
+      <c r="T57" s="244"/>
+      <c r="U57" s="244"/>
+      <c r="V57" s="244"/>
+      <c r="W57" s="244"/>
+      <c r="X57" s="244"/>
+      <c r="Y57" s="244"/>
+      <c r="Z57" s="244"/>
+    </row>
+    <row r="58" spans="1:26" s="245" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="248" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" s="173"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="192">
+        <v>60900</v>
+      </c>
+      <c r="E58" s="150" t="s">
+        <v>183</v>
+      </c>
+      <c r="F58" s="244"/>
+      <c r="G58" s="244"/>
+      <c r="H58" s="244"/>
+      <c r="I58" s="244"/>
+      <c r="J58" s="244"/>
+      <c r="K58" s="244"/>
+      <c r="L58" s="244"/>
+      <c r="M58" s="244"/>
+      <c r="N58" s="244"/>
+      <c r="O58" s="244"/>
+      <c r="P58" s="244"/>
+      <c r="Q58" s="244"/>
+      <c r="R58" s="244"/>
+      <c r="S58" s="244"/>
+      <c r="T58" s="244"/>
+      <c r="U58" s="244"/>
+      <c r="V58" s="244"/>
+      <c r="W58" s="244"/>
+      <c r="X58" s="244"/>
+      <c r="Y58" s="244"/>
+      <c r="Z58" s="244"/>
+    </row>
+    <row r="59" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="139" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" s="138"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="250">
         <v>19588.650000000001</v>
       </c>
-      <c r="E56" s="163" t="s">
-        <v>38</v>
-      </c>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="50"/>
-    </row>
-    <row r="57" spans="1:26" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="225" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="226"/>
-      <c r="C57" s="49"/>
-      <c r="D57" s="204"/>
-      <c r="E57" s="150"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="50"/>
-    </row>
-    <row r="58" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="225" t="s">
-        <v>178</v>
-      </c>
-      <c r="B58" s="226"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="205">
-        <v>93772.25</v>
-      </c>
-      <c r="E58" s="150" t="s">
+      <c r="E59" s="163" t="s">
+        <v>179</v>
+      </c>
+      <c r="F59" s="50"/>
+      <c r="G59" s="50"/>
+      <c r="H59" s="50"/>
+    </row>
+    <row r="60" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="214" t="s">
+        <v>34</v>
+      </c>
+      <c r="B60" s="215"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="193">
+        <v>80080</v>
+      </c>
+      <c r="E60" s="150" t="s">
+        <v>176</v>
+      </c>
+      <c r="F60" s="50"/>
+      <c r="G60" s="50"/>
+      <c r="H60" s="50"/>
+    </row>
+    <row r="61" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="214" t="s">
+        <v>169</v>
+      </c>
+      <c r="B61" s="215"/>
+      <c r="C61" s="33"/>
+      <c r="D61" s="187">
+        <v>201284.99</v>
+      </c>
+      <c r="E61" s="150" t="s">
+        <v>180</v>
+      </c>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+    </row>
+    <row r="62" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="214" t="s">
         <v>35</v>
       </c>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
-      <c r="H58" s="50"/>
-    </row>
-    <row r="59" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="225" t="s">
-        <v>179</v>
-      </c>
-      <c r="B59" s="226"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="258">
-        <v>201284.99</v>
-      </c>
-      <c r="E59" s="150" t="s">
-        <v>35</v>
-      </c>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="4"/>
-      <c r="S59" s="4"/>
-      <c r="T59" s="4"/>
-      <c r="U59" s="4"/>
-      <c r="V59" s="4"/>
-      <c r="W59" s="4"/>
-      <c r="X59" s="4"/>
-      <c r="Y59" s="4"/>
-      <c r="Z59" s="4"/>
-    </row>
-    <row r="60" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="225" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="226"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="198"/>
-      <c r="E60" s="164"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="39"/>
-    </row>
-    <row r="61" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="25"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="199"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-    </row>
-    <row r="62" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="234"/>
-      <c r="B62" s="226"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="199"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="4"/>
-      <c r="T62" s="4"/>
-      <c r="U62" s="4"/>
-      <c r="V62" s="4"/>
-      <c r="W62" s="4"/>
-      <c r="X62" s="4"/>
-      <c r="Y62" s="4"/>
-      <c r="Z62" s="4"/>
+      <c r="B62" s="215"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="187"/>
+      <c r="E62" s="164"/>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39"/>
     </row>
     <row r="63" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="25"/>
-      <c r="B63" s="51"/>
+      <c r="B63" s="25"/>
       <c r="C63" s="25"/>
-      <c r="D63" s="199"/>
-      <c r="E63" s="52"/>
+      <c r="D63" s="188"/>
+      <c r="E63" s="48"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4"/>
-      <c r="U63" s="4"/>
-      <c r="V63" s="4"/>
-      <c r="W63" s="4"/>
-      <c r="X63" s="4"/>
-      <c r="Y63" s="4"/>
-      <c r="Z63" s="4"/>
     </row>
     <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="225"/>
-      <c r="B64" s="227"/>
-      <c r="C64" s="53"/>
-      <c r="D64" s="232"/>
-      <c r="E64" s="241"/>
+      <c r="A64" s="226"/>
+      <c r="B64" s="215"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="188"/>
+      <c r="E64" s="48"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
@@ -3231,12 +3252,12 @@
       <c r="Y64" s="4"/>
       <c r="Z64" s="4"/>
     </row>
-    <row r="65" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="228"/>
-      <c r="B65" s="229"/>
-      <c r="C65" s="53"/>
-      <c r="D65" s="233"/>
-      <c r="E65" s="233"/>
+    <row r="65" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="25"/>
+      <c r="B65" s="51"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="188"/>
+      <c r="E65" s="52"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
@@ -3259,12 +3280,12 @@
       <c r="Y65" s="4"/>
       <c r="Z65" s="4"/>
     </row>
-    <row r="66" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="225"/>
-      <c r="B66" s="226"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="206"/>
-      <c r="E66" s="54"/>
+    <row r="66" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="214"/>
+      <c r="B66" s="220"/>
+      <c r="C66" s="53"/>
+      <c r="D66" s="225"/>
+      <c r="E66" s="217"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
@@ -3287,12 +3308,12 @@
       <c r="Y66" s="4"/>
       <c r="Z66" s="4"/>
     </row>
-    <row r="67" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="225"/>
-      <c r="B67" s="226"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="206"/>
-      <c r="E67" s="54"/>
+    <row r="67" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="221"/>
+      <c r="B67" s="222"/>
+      <c r="C67" s="53"/>
+      <c r="D67" s="218"/>
+      <c r="E67" s="218"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
@@ -3315,19 +3336,40 @@
       <c r="Y67" s="4"/>
       <c r="Z67" s="4"/>
     </row>
-    <row r="68" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="225"/>
-      <c r="B68" s="226"/>
+    <row r="68" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="214"/>
+      <c r="B68" s="215"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="206"/>
-      <c r="E68" s="48"/>
-    </row>
-    <row r="69" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="25"/>
-      <c r="B69" s="55"/>
+      <c r="D68" s="194"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="4"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+    </row>
+    <row r="69" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="214"/>
+      <c r="B69" s="215"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="206"/>
-      <c r="E69" s="48"/>
+      <c r="D69" s="194"/>
+      <c r="E69" s="54"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
@@ -3350,39 +3392,18 @@
       <c r="Y69" s="4"/>
       <c r="Z69" s="4"/>
     </row>
-    <row r="70" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="225"/>
-      <c r="B70" s="226"/>
+    <row r="70" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="214"/>
+      <c r="B70" s="215"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="206"/>
+      <c r="D70" s="194"/>
       <c r="E70" s="48"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-      <c r="T70" s="4"/>
-      <c r="U70" s="4"/>
-      <c r="V70" s="4"/>
-      <c r="W70" s="4"/>
-      <c r="X70" s="4"/>
-      <c r="Y70" s="4"/>
-      <c r="Z70" s="4"/>
     </row>
     <row r="71" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="51"/>
-      <c r="B71" s="56"/>
+      <c r="A71" s="25"/>
+      <c r="B71" s="55"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="206"/>
+      <c r="D71" s="194"/>
       <c r="E71" s="48"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
@@ -3406,12 +3427,12 @@
       <c r="Y71" s="4"/>
       <c r="Z71" s="4"/>
     </row>
-    <row r="72" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="225"/>
-      <c r="B72" s="226"/>
+    <row r="72" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="214"/>
+      <c r="B72" s="215"/>
       <c r="C72" s="25"/>
-      <c r="D72" s="206"/>
-      <c r="E72" s="57"/>
+      <c r="D72" s="194"/>
+      <c r="E72" s="48"/>
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
@@ -3434,12 +3455,12 @@
       <c r="Y72" s="4"/>
       <c r="Z72" s="4"/>
     </row>
-    <row r="73" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="225"/>
-      <c r="B73" s="226"/>
+    <row r="73" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="51"/>
+      <c r="B73" s="56"/>
       <c r="C73" s="25"/>
-      <c r="D73" s="206"/>
-      <c r="E73" s="57"/>
+      <c r="D73" s="194"/>
+      <c r="E73" s="48"/>
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
@@ -3462,11 +3483,11 @@
       <c r="Y73" s="4"/>
       <c r="Z73" s="4"/>
     </row>
-    <row r="74" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="236"/>
-      <c r="B74" s="226"/>
-      <c r="C74" s="58"/>
-      <c r="D74" s="206"/>
+    <row r="74" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="214"/>
+      <c r="B74" s="215"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="194"/>
       <c r="E74" s="57"/>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
@@ -3490,160 +3511,150 @@
       <c r="Y74" s="4"/>
       <c r="Z74" s="4"/>
     </row>
-    <row r="75" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="196"/>
-      <c r="E75" s="40">
-        <f>SUM(D54:D60)</f>
-        <v>438645.89</v>
-      </c>
-    </row>
-    <row r="76" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="29"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="196"/>
-      <c r="E76" s="59"/>
-    </row>
-    <row r="77" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="225"/>
-      <c r="B77" s="226"/>
-      <c r="C77" s="60"/>
-      <c r="D77" s="201"/>
-      <c r="E77" s="57"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
-      <c r="T77" s="4"/>
-      <c r="U77" s="4"/>
-      <c r="V77" s="4"/>
-      <c r="W77" s="4"/>
-      <c r="X77" s="4"/>
-      <c r="Y77" s="4"/>
-      <c r="Z77" s="4"/>
-    </row>
-    <row r="78" spans="1:26" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="225"/>
-      <c r="B78" s="226"/>
-      <c r="C78" s="61"/>
-      <c r="D78" s="201"/>
-      <c r="E78" s="62"/>
-    </row>
-    <row r="79" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="236"/>
-      <c r="B79" s="226"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="201"/>
-      <c r="E79" s="62"/>
-    </row>
-    <row r="80" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="25"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="201"/>
+    <row r="75" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="214"/>
+      <c r="B75" s="215"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="194"/>
+      <c r="E75" s="57"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+      <c r="T75" s="4"/>
+      <c r="U75" s="4"/>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+    </row>
+    <row r="76" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="216"/>
+      <c r="B76" s="215"/>
+      <c r="C76" s="58"/>
+      <c r="D76" s="194"/>
+      <c r="E76" s="57"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+      <c r="T76" s="4"/>
+      <c r="U76" s="4"/>
+      <c r="V76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+    </row>
+    <row r="77" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="185"/>
+      <c r="E77" s="40">
+        <f>SUM(D55:D62)</f>
+        <v>612853.64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
+      <c r="D78" s="185"/>
+      <c r="E78" s="59"/>
+    </row>
+    <row r="79" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="214"/>
+      <c r="B79" s="215"/>
+      <c r="C79" s="60"/>
+      <c r="D79" s="190"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+      <c r="S79" s="4"/>
+      <c r="T79" s="4"/>
+      <c r="U79" s="4"/>
+      <c r="V79" s="4"/>
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+    </row>
+    <row r="80" spans="1:26" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="214"/>
+      <c r="B80" s="215"/>
+      <c r="C80" s="61"/>
+      <c r="D80" s="190"/>
       <c r="E80" s="62"/>
     </row>
-    <row r="81" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="25"/>
-      <c r="B81" s="25"/>
+    <row r="81" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="216"/>
+      <c r="B81" s="215"/>
       <c r="C81" s="25"/>
-      <c r="D81" s="201"/>
-      <c r="E81" s="63"/>
-    </row>
-    <row r="82" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="B82" s="24"/>
-      <c r="C82" s="24"/>
-      <c r="D82" s="207"/>
-      <c r="E82" s="64">
-        <f>SUM(D77:D81)</f>
-        <v>0</v>
-      </c>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
-      <c r="O82" s="4"/>
-      <c r="P82" s="4"/>
-      <c r="Q82" s="4"/>
-      <c r="R82" s="4"/>
-      <c r="S82" s="4"/>
-      <c r="T82" s="4"/>
-      <c r="U82" s="4"/>
-      <c r="V82" s="4"/>
-      <c r="W82" s="4"/>
-      <c r="X82" s="4"/>
-      <c r="Y82" s="4"/>
-      <c r="Z82" s="4"/>
-    </row>
-    <row r="83" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="B83" s="65"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="194"/>
-      <c r="E83" s="59">
-        <f>850.17+698.43+4797.54+618.63+2.1+2364+10+1202.53+1583.5+3434+961.5+2275.93+1316.37+1224+2364.03+534+4200+154.8+1600+1200+2351.5+457.76+2442+6000</f>
-        <v>42642.79</v>
-      </c>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
-      <c r="L83" s="4"/>
-      <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
-      <c r="O83" s="4"/>
-      <c r="P83" s="4"/>
-      <c r="Q83" s="4"/>
-      <c r="R83" s="4"/>
-      <c r="S83" s="4"/>
-      <c r="T83" s="4"/>
-      <c r="U83" s="4"/>
-      <c r="V83" s="4"/>
-      <c r="W83" s="4"/>
-      <c r="X83" s="4"/>
-      <c r="Y83" s="4"/>
-      <c r="Z83" s="4"/>
-    </row>
-    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B84" s="25"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="220">
-        <f>21359.46</f>
-        <v>21359.46</v>
-      </c>
-      <c r="E84" s="66"/>
+      <c r="D81" s="190"/>
+      <c r="E81" s="62"/>
+    </row>
+    <row r="82" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="25"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="25"/>
+      <c r="D82" s="190"/>
+      <c r="E82" s="62"/>
+    </row>
+    <row r="83" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="25"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="190"/>
+      <c r="E83" s="63"/>
+    </row>
+    <row r="84" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B84" s="24"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="195"/>
+      <c r="E84" s="64">
+        <f>SUM(D79:D83)</f>
+        <v>0</v>
+      </c>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
@@ -3666,16 +3677,17 @@
       <c r="Y84" s="4"/>
       <c r="Z84" s="4"/>
     </row>
-    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B85" s="25"/>
-      <c r="C85" s="25"/>
-      <c r="D85" s="199">
-        <v>24000</v>
-      </c>
-      <c r="E85" s="54"/>
+    <row r="85" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B85" s="65"/>
+      <c r="C85" s="29"/>
+      <c r="D85" s="183"/>
+      <c r="E85" s="59">
+        <f>850.17+698.43+4797.54+618.63+2.1+2364+10+1202.53+1583.5+3434+961.5+2275.93+1316.37+1224+2364.03+534+4200+154.8+1600+1200+2351.5+457.76+2442+6000</f>
+        <v>42642.79</v>
+      </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
@@ -3699,124 +3711,133 @@
       <c r="Z85" s="4"/>
     </row>
     <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="67" t="s">
-        <v>21</v>
-      </c>
-      <c r="B86" s="67"/>
-      <c r="C86" s="67"/>
-      <c r="D86" s="159"/>
-      <c r="E86" s="40">
-        <f>SUM(D84:D85)</f>
-        <v>45359.46</v>
-      </c>
+      <c r="A86" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="207">
+        <f>20294.13+3493.04</f>
+        <v>23787.170000000002</v>
+      </c>
+      <c r="E86" s="66"/>
       <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="4"/>
+      <c r="Q86" s="4"/>
+      <c r="R86" s="4"/>
+      <c r="S86" s="4"/>
+      <c r="T86" s="4"/>
+      <c r="U86" s="4"/>
+      <c r="V86" s="4"/>
+      <c r="W86" s="4"/>
+      <c r="X86" s="4"/>
+      <c r="Y86" s="4"/>
+      <c r="Z86" s="4"/>
     </row>
     <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="25"/>
+      <c r="A87" s="25" t="s">
+        <v>40</v>
+      </c>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
-      <c r="D87" s="25"/>
-      <c r="E87" s="68"/>
+      <c r="D87" s="188">
+        <v>24000</v>
+      </c>
+      <c r="E87" s="54"/>
       <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="4"/>
+      <c r="R87" s="4"/>
+      <c r="S87" s="4"/>
+      <c r="T87" s="4"/>
+      <c r="U87" s="4"/>
+      <c r="V87" s="4"/>
+      <c r="W87" s="4"/>
+      <c r="X87" s="4"/>
+      <c r="Y87" s="4"/>
+      <c r="Z87" s="4"/>
     </row>
     <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="69" t="s">
-        <v>46</v>
-      </c>
-      <c r="B88" s="69"/>
-      <c r="C88" s="69"/>
-      <c r="D88" s="70"/>
-      <c r="E88" s="71">
-        <v>1000000</v>
+      <c r="A88" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" s="67"/>
+      <c r="C88" s="67"/>
+      <c r="D88" s="159"/>
+      <c r="E88" s="40">
+        <f>SUM(D86:D87)</f>
+        <v>47787.17</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="72"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="73"/>
-      <c r="F89" s="74"/>
+      <c r="A89" s="25"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="68"/>
+      <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="B90" s="76"/>
-      <c r="C90" s="77"/>
-      <c r="D90" s="77"/>
-      <c r="E90" s="78">
-        <f>(SUM(E31:E88))</f>
-        <v>2689010.96</v>
+      <c r="A90" s="69" t="s">
+        <v>181</v>
+      </c>
+      <c r="B90" s="69"/>
+      <c r="C90" s="69"/>
+      <c r="D90" s="70"/>
+      <c r="E90" s="71">
+        <v>747677.2</v>
       </c>
       <c r="F90" s="4"/>
     </row>
-    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
+    <row r="91" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="72"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="73"/>
+      <c r="F91" s="74"/>
+    </row>
+    <row r="92" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" s="76"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
+      <c r="E92" s="78">
+        <f>(SUM(E31:E90))</f>
+        <v>2818059.9699999997</v>
+      </c>
       <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
-      <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
-      <c r="V92" s="4"/>
-      <c r="W92" s="4"/>
-      <c r="X92" s="4"/>
-      <c r="Y92" s="4"/>
-      <c r="Z92" s="4"/>
-    </row>
-    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B93" s="20"/>
-      <c r="C93" s="21"/>
-      <c r="D93" s="22"/>
-      <c r="E93" s="23"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
-      <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="4"/>
-      <c r="X93" s="4"/>
-      <c r="Y93" s="4"/>
-      <c r="Z93" s="4"/>
-    </row>
+      <c r="G92" s="264"/>
+      <c r="H92" s="106"/>
+    </row>
+    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="154"/>
-      <c r="B94" s="154"/>
-      <c r="C94" s="153"/>
-      <c r="D94" s="44"/>
-      <c r="E94" s="62"/>
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
@@ -3840,13 +3861,13 @@
       <c r="Z94" s="4"/>
     </row>
     <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="154"/>
-      <c r="B95" s="154"/>
-      <c r="C95" s="153"/>
-      <c r="D95" s="44">
-        <v>0</v>
-      </c>
-      <c r="E95" s="44"/>
+      <c r="A95" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B95" s="20"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="22"/>
+      <c r="E95" s="23"/>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
@@ -3870,16 +3891,11 @@
       <c r="Z95" s="4"/>
     </row>
     <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="79" t="s">
-        <v>43</v>
-      </c>
-      <c r="B96" s="80"/>
-      <c r="C96" s="80"/>
-      <c r="D96" s="81"/>
-      <c r="E96" s="81">
-        <f>SUM(D94:D95)</f>
-        <v>0</v>
-      </c>
+      <c r="A96" s="154"/>
+      <c r="B96" s="154"/>
+      <c r="C96" s="153"/>
+      <c r="D96" s="44"/>
+      <c r="E96" s="62"/>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
@@ -3902,12 +3918,14 @@
       <c r="Y96" s="4"/>
       <c r="Z96" s="4"/>
     </row>
-    <row r="97" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
+    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="154"/>
+      <c r="B97" s="154"/>
+      <c r="C97" s="153"/>
+      <c r="D97" s="44">
+        <v>0</v>
+      </c>
+      <c r="E97" s="44"/>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
@@ -3930,12 +3948,17 @@
       <c r="Y97" s="4"/>
       <c r="Z97" s="4"/>
     </row>
-    <row r="98" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
+    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B98" s="80"/>
+      <c r="C98" s="80"/>
+      <c r="D98" s="81"/>
+      <c r="E98" s="81">
+        <f>SUM(D96:D97)</f>
+        <v>0</v>
+      </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
@@ -3958,14 +3981,12 @@
       <c r="Y98" s="4"/>
       <c r="Z98" s="4"/>
     </row>
-    <row r="99" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="B99" s="69"/>
-      <c r="C99" s="69"/>
-      <c r="D99" s="70"/>
-      <c r="E99" s="82"/>
+    <row r="99" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
@@ -3988,7 +4009,7 @@
       <c r="Y99" s="4"/>
       <c r="Z99" s="4"/>
     </row>
-    <row r="100" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -4016,17 +4037,14 @@
       <c r="Y100" s="4"/>
       <c r="Z100" s="4"/>
     </row>
-    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="75" t="s">
-        <v>50</v>
-      </c>
-      <c r="B101" s="76"/>
-      <c r="C101" s="77"/>
-      <c r="D101" s="77"/>
-      <c r="E101" s="78">
-        <f>E96+E99</f>
-        <v>0</v>
-      </c>
+    <row r="101" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="B101" s="69"/>
+      <c r="C101" s="69"/>
+      <c r="D101" s="70"/>
+      <c r="E101" s="82"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
@@ -4049,7 +4067,7 @@
       <c r="Y101" s="4"/>
       <c r="Z101" s="4"/>
     </row>
-    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4078,16 +4096,16 @@
       <c r="Z102" s="4"/>
     </row>
     <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="83" t="s">
-        <v>51</v>
-      </c>
-      <c r="B103" s="84">
-        <f>E90</f>
-        <v>2689010.96</v>
-      </c>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
+      <c r="A103" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="B103" s="76"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="78">
+        <f>E98+E101</f>
+        <v>0</v>
+      </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
@@ -4111,21 +4129,40 @@
       <c r="Z103" s="4"/>
     </row>
     <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="83" t="s">
-        <v>52</v>
-      </c>
-      <c r="B104" s="84">
-        <f>E90-E88</f>
-        <v>1689010.96</v>
-      </c>
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="4"/>
+      <c r="S104" s="4"/>
+      <c r="T104" s="4"/>
+      <c r="U104" s="4"/>
+      <c r="V104" s="4"/>
+      <c r="W104" s="4"/>
+      <c r="X104" s="4"/>
+      <c r="Y104" s="4"/>
+      <c r="Z104" s="4"/>
     </row>
     <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="83" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B105" s="84">
-        <f>E101-E99</f>
-        <v>0</v>
+        <f>E92</f>
+        <v>2818059.9699999997</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
@@ -4154,66 +4191,92 @@
     </row>
     <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="83" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B106" s="84">
-        <f>E101</f>
-        <v>0</v>
-      </c>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="4"/>
-      <c r="L106" s="4"/>
-      <c r="M106" s="4"/>
-      <c r="N106" s="4"/>
-      <c r="O106" s="4"/>
-      <c r="P106" s="4"/>
-      <c r="Q106" s="4"/>
-      <c r="R106" s="4"/>
-      <c r="S106" s="4"/>
-      <c r="T106" s="4"/>
-      <c r="U106" s="4"/>
-      <c r="V106" s="4"/>
-      <c r="W106" s="4"/>
-      <c r="X106" s="4"/>
-      <c r="Y106" s="4"/>
-      <c r="Z106" s="4"/>
+        <f>E92-E90</f>
+        <v>2070382.7699999998</v>
+      </c>
     </row>
     <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
+      <c r="A107" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="B107" s="84">
+        <f>E103-E101</f>
+        <v>0</v>
+      </c>
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="4"/>
+      <c r="T107" s="4"/>
+      <c r="U107" s="4"/>
+      <c r="V107" s="4"/>
+      <c r="W107" s="4"/>
+      <c r="X107" s="4"/>
+      <c r="Y107" s="4"/>
+      <c r="Z107" s="4"/>
     </row>
     <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
+      <c r="A108" s="83" t="s">
+        <v>48</v>
+      </c>
+      <c r="B108" s="84">
+        <f>E103</f>
+        <v>0</v>
+      </c>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="4"/>
+      <c r="S108" s="4"/>
+      <c r="T108" s="4"/>
+      <c r="U108" s="4"/>
+      <c r="V108" s="4"/>
+      <c r="W108" s="4"/>
+      <c r="X108" s="4"/>
+      <c r="Y108" s="4"/>
+      <c r="Z108" s="4"/>
     </row>
     <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="237" t="s">
-        <v>55</v>
-      </c>
-      <c r="B109" s="223"/>
-      <c r="C109" s="223"/>
-      <c r="D109" s="223"/>
-      <c r="E109" s="223"/>
-    </row>
-    <row r="110" spans="1:26" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="223"/>
-      <c r="B110" s="223"/>
-      <c r="C110" s="223"/>
-      <c r="D110" s="223"/>
-      <c r="E110" s="223"/>
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+    </row>
+    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
     </row>
     <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4"/>
@@ -4231,70 +4294,46 @@
     </row>
     <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="144" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B113" s="145"/>
       <c r="C113" s="85"/>
     </row>
     <row r="114" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="148" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B114" s="149">
-        <v>-461852.87000000098</v>
+        <v>-615293.43000000063</v>
       </c>
       <c r="C114" s="86"/>
     </row>
     <row r="115" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="146" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B115" s="147">
         <f>'Copia de PRORRATEO'!H37</f>
-        <v>1664619.4100000001</v>
+        <v>2663365.1799999997</v>
       </c>
       <c r="C115" s="85"/>
     </row>
-    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="87" t="s">
-        <v>59</v>
-      </c>
-      <c r="B116" s="88">
-        <f>B139</f>
-        <v>0</v>
-      </c>
-      <c r="C116" s="85"/>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
-      <c r="H116" s="4"/>
-      <c r="I116" s="4"/>
-      <c r="J116" s="4"/>
-      <c r="K116" s="4"/>
-      <c r="L116" s="4"/>
-      <c r="M116" s="4"/>
-      <c r="N116" s="4"/>
-      <c r="O116" s="4"/>
-      <c r="P116" s="4"/>
-      <c r="Q116" s="4"/>
-      <c r="R116" s="4"/>
-      <c r="S116" s="4"/>
-      <c r="T116" s="4"/>
-      <c r="U116" s="4"/>
-      <c r="V116" s="4"/>
-      <c r="W116" s="4"/>
-      <c r="X116" s="4"/>
-      <c r="Y116" s="4"/>
-      <c r="Z116" s="4"/>
+    <row r="116" spans="1:26" s="245" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="B116" s="247">
+        <v>-6918</v>
+      </c>
+      <c r="C116" s="246"/>
     </row>
     <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="89" t="s">
-        <v>60</v>
+      <c r="A117" s="87" t="s">
+        <v>52</v>
       </c>
       <c r="B117" s="88">
-        <f>-B104</f>
-        <v>-1689010.96</v>
+        <f>B140</f>
+        <v>0</v>
       </c>
       <c r="C117" s="85"/>
       <c r="D117" s="4"/>
@@ -4322,18 +4361,46 @@
       <c r="Z117" s="4"/>
     </row>
     <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="90" t="s">
-        <v>61</v>
+      <c r="A118" s="89" t="s">
+        <v>53</v>
       </c>
       <c r="B118" s="88">
-        <f>-(B105)</f>
-        <v>0</v>
+        <f>-B106</f>
+        <v>-2070382.7699999998</v>
       </c>
       <c r="C118" s="85"/>
-    </row>
-    <row r="119" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="90"/>
-      <c r="B119" s="88"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+      <c r="N118" s="4"/>
+      <c r="O118" s="4"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="4"/>
+      <c r="R118" s="4"/>
+      <c r="S118" s="4"/>
+      <c r="T118" s="4"/>
+      <c r="U118" s="4"/>
+      <c r="V118" s="4"/>
+      <c r="W118" s="4"/>
+      <c r="X118" s="4"/>
+      <c r="Y118" s="4"/>
+      <c r="Z118" s="4"/>
+    </row>
+    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="90" t="s">
+        <v>54</v>
+      </c>
+      <c r="B119" s="88">
+        <f>-(B107)</f>
+        <v>0</v>
+      </c>
       <c r="C119" s="85"/>
     </row>
     <row r="120" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4341,83 +4408,58 @@
       <c r="B120" s="88"/>
       <c r="C120" s="85"/>
     </row>
-    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="B121" s="92">
-        <f>SUM(B114:B120)</f>
-        <v>-486244.42000000086</v>
-      </c>
-      <c r="C121" s="93"/>
+    <row r="121" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="90"/>
+      <c r="B121" s="88"/>
+      <c r="C121" s="85"/>
     </row>
     <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
-      <c r="B122" s="74"/>
+      <c r="A122" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="B122" s="92">
+        <f>SUM(B114:B121)</f>
+        <v>-29229.020000000717</v>
+      </c>
       <c r="C122" s="93"/>
-      <c r="D122" s="74"/>
-      <c r="E122" s="4"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-      <c r="I122" s="4"/>
-      <c r="J122" s="4"/>
-      <c r="K122" s="4"/>
-      <c r="L122" s="4"/>
-      <c r="M122" s="4"/>
-      <c r="N122" s="4"/>
-      <c r="O122" s="4"/>
-      <c r="P122" s="4"/>
-      <c r="Q122" s="4"/>
-      <c r="R122" s="4"/>
-      <c r="S122" s="4"/>
-      <c r="T122" s="4"/>
-      <c r="U122" s="4"/>
-      <c r="V122" s="4"/>
-      <c r="W122" s="4"/>
-      <c r="X122" s="4"/>
-      <c r="Y122" s="4"/>
-      <c r="Z122" s="4"/>
-    </row>
-    <row r="123" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4"/>
-      <c r="B123" s="94"/>
+      <c r="B123" s="74"/>
       <c r="C123" s="93"/>
-    </row>
-    <row r="124" spans="1:26" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="74"/>
-      <c r="C124" s="95"/>
-      <c r="D124" s="39"/>
-      <c r="E124" s="39"/>
-      <c r="F124" s="39"/>
-      <c r="G124" s="39"/>
-      <c r="H124" s="39"/>
-      <c r="I124" s="39"/>
-      <c r="J124" s="39"/>
-      <c r="K124" s="39"/>
-      <c r="L124" s="39"/>
-      <c r="M124" s="39"/>
-      <c r="N124" s="39"/>
-      <c r="O124" s="39"/>
-      <c r="P124" s="39"/>
-      <c r="Q124" s="39"/>
-      <c r="R124" s="39"/>
-      <c r="S124" s="39"/>
-      <c r="T124" s="39"/>
-      <c r="U124" s="39"/>
-      <c r="V124" s="39"/>
-      <c r="W124" s="39"/>
-      <c r="X124" s="39"/>
-      <c r="Y124" s="39"/>
-      <c r="Z124" s="39"/>
+      <c r="D123" s="74"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
+      <c r="I123" s="4"/>
+      <c r="J123" s="4"/>
+      <c r="K123" s="4"/>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4"/>
+      <c r="N123" s="4"/>
+      <c r="O123" s="4"/>
+      <c r="P123" s="4"/>
+      <c r="Q123" s="4"/>
+      <c r="R123" s="4"/>
+      <c r="S123" s="4"/>
+      <c r="T123" s="4"/>
+      <c r="U123" s="4"/>
+      <c r="V123" s="4"/>
+      <c r="W123" s="4"/>
+      <c r="X123" s="4"/>
+      <c r="Y123" s="4"/>
+      <c r="Z123" s="4"/>
+    </row>
+    <row r="124" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="4"/>
+      <c r="B124" s="94"/>
+      <c r="C124" s="93"/>
     </row>
     <row r="125" spans="1:26" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="96" t="s">
-        <v>62</v>
-      </c>
-      <c r="B125" s="44"/>
+      <c r="B125" s="74"/>
       <c r="C125" s="95"/>
-      <c r="D125" s="97"/>
+      <c r="D125" s="39"/>
       <c r="E125" s="39"/>
       <c r="F125" s="39"/>
       <c r="G125" s="39"/>
@@ -4442,14 +4484,12 @@
       <c r="Z125" s="39"/>
     </row>
     <row r="126" spans="1:26" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B126" s="44">
-        <v>0</v>
-      </c>
+      <c r="A126" s="96" t="s">
+        <v>55</v>
+      </c>
+      <c r="B126" s="44"/>
       <c r="C126" s="95"/>
-      <c r="D126" s="39"/>
+      <c r="D126" s="97"/>
       <c r="E126" s="39"/>
       <c r="F126" s="39"/>
       <c r="G126" s="39"/>
@@ -4473,107 +4513,109 @@
       <c r="Y126" s="39"/>
       <c r="Z126" s="39"/>
     </row>
-    <row r="127" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="25" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B127" s="44">
         <v>0</v>
       </c>
-      <c r="C127" s="93"/>
-      <c r="D127" s="74"/>
-    </row>
-    <row r="128" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C127" s="95"/>
+      <c r="D127" s="39"/>
+      <c r="E127" s="39"/>
+      <c r="F127" s="39"/>
+      <c r="G127" s="39"/>
+      <c r="H127" s="39"/>
+      <c r="I127" s="39"/>
+      <c r="J127" s="39"/>
+      <c r="K127" s="39"/>
+      <c r="L127" s="39"/>
+      <c r="M127" s="39"/>
+      <c r="N127" s="39"/>
+      <c r="O127" s="39"/>
+      <c r="P127" s="39"/>
+      <c r="Q127" s="39"/>
+      <c r="R127" s="39"/>
+      <c r="S127" s="39"/>
+      <c r="T127" s="39"/>
+      <c r="U127" s="39"/>
+      <c r="V127" s="39"/>
+      <c r="W127" s="39"/>
+      <c r="X127" s="39"/>
+      <c r="Y127" s="39"/>
+      <c r="Z127" s="39"/>
+    </row>
+    <row r="128" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B128" s="44">
         <v>0</v>
       </c>
       <c r="C128" s="93"/>
+      <c r="D128" s="74"/>
     </row>
     <row r="129" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="25" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B129" s="44">
         <v>0</v>
       </c>
-      <c r="C129" s="98"/>
+      <c r="C129" s="93"/>
     </row>
     <row r="130" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="96" t="s">
-        <v>65</v>
-      </c>
-      <c r="B130" s="99">
-        <f>SUM(B126:B129)</f>
-        <v>0</v>
-      </c>
-      <c r="C130" s="85"/>
-    </row>
-    <row r="131" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="231" t="s">
-        <v>66</v>
-      </c>
-      <c r="B133" s="223"/>
-      <c r="C133" s="223"/>
-    </row>
+      <c r="A130" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B130" s="44">
+        <v>0</v>
+      </c>
+      <c r="C130" s="98"/>
+    </row>
+    <row r="131" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="96" t="s">
+        <v>58</v>
+      </c>
+      <c r="B131" s="99">
+        <f>SUM(B127:B130)</f>
+        <v>0</v>
+      </c>
+      <c r="C131" s="85"/>
+    </row>
+    <row r="132" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="223"/>
-      <c r="B134" s="223"/>
-      <c r="C134" s="223"/>
+      <c r="A134" s="224" t="s">
+        <v>59</v>
+      </c>
+      <c r="B134" s="209"/>
+      <c r="C134" s="209"/>
     </row>
     <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="25"/>
-      <c r="B135" s="176"/>
-      <c r="C135" s="44">
-        <v>11948.17</v>
-      </c>
+      <c r="A135" s="209"/>
+      <c r="B135" s="209"/>
+      <c r="C135" s="209"/>
     </row>
     <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="25"/>
-      <c r="B136" s="177"/>
+      <c r="B136" s="176"/>
       <c r="C136" s="44">
-        <v>52000</v>
+        <v>11948.17</v>
       </c>
     </row>
     <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="100"/>
+      <c r="A137" s="25"/>
       <c r="B137" s="177"/>
       <c r="C137" s="44">
-        <v>61209</v>
-      </c>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
-      <c r="K137" s="4"/>
-      <c r="L137" s="4"/>
-      <c r="M137" s="4"/>
-      <c r="N137" s="4"/>
-      <c r="O137" s="4"/>
-      <c r="P137" s="4"/>
-      <c r="Q137" s="4"/>
-      <c r="R137" s="4"/>
-      <c r="S137" s="4"/>
-      <c r="T137" s="4"/>
-      <c r="U137" s="4"/>
-      <c r="V137" s="4"/>
-      <c r="W137" s="4"/>
-      <c r="X137" s="4"/>
-      <c r="Y137" s="4"/>
-      <c r="Z137" s="4"/>
+        <v>52000</v>
+      </c>
     </row>
     <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="87"/>
+      <c r="A138" s="100"/>
       <c r="B138" s="177"/>
       <c r="C138" s="44">
-        <v>40000</v>
+        <v>61209</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
@@ -4600,19 +4642,48 @@
       <c r="Z138" s="4"/>
     </row>
     <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="101" t="s">
-        <v>43</v>
-      </c>
-      <c r="B139" s="178">
-        <f>SUM(B135:B138)</f>
-        <v>0</v>
-      </c>
-      <c r="C139" s="102"/>
+      <c r="A139" s="87"/>
+      <c r="B139" s="177"/>
+      <c r="C139" s="44">
+        <v>40000</v>
+      </c>
+      <c r="D139" s="4"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4"/>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4"/>
+      <c r="I139" s="4"/>
+      <c r="J139" s="4"/>
+      <c r="K139" s="4"/>
+      <c r="L139" s="4"/>
+      <c r="M139" s="4"/>
+      <c r="N139" s="4"/>
+      <c r="O139" s="4"/>
+      <c r="P139" s="4"/>
+      <c r="Q139" s="4"/>
+      <c r="R139" s="4"/>
+      <c r="S139" s="4"/>
+      <c r="T139" s="4"/>
+      <c r="U139" s="4"/>
+      <c r="V139" s="4"/>
+      <c r="W139" s="4"/>
+      <c r="X139" s="4"/>
+      <c r="Y139" s="4"/>
+      <c r="Z139" s="4"/>
     </row>
     <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M140" s="103"/>
-    </row>
-    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A140" s="101" t="s">
+        <v>38</v>
+      </c>
+      <c r="B140" s="178">
+        <f>SUM(B136:B139)</f>
+        <v>0</v>
+      </c>
+      <c r="C140" s="102"/>
+    </row>
+    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M141" s="103"/>
+    </row>
     <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5478,37 +5549,36 @@
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A109:E110"/>
+  <mergeCells count="24">
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A66:B67"/>
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A134:C135"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A64:B65"/>
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A133:C134"/>
-    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="E66:E67"/>
     <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A54:B54"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5545,16 +5615,16 @@
       <c r="C1" s="104"/>
       <c r="D1" s="104"/>
       <c r="E1" s="104"/>
-      <c r="F1" s="252"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="223"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="223"/>
-      <c r="L1" s="223"/>
-      <c r="M1" s="223"/>
-      <c r="N1" s="223"/>
-      <c r="O1" s="223"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="209"/>
+      <c r="H1" s="209"/>
+      <c r="I1" s="209"/>
+      <c r="J1" s="209"/>
+      <c r="K1" s="209"/>
+      <c r="L1" s="209"/>
+      <c r="M1" s="209"/>
+      <c r="N1" s="209"/>
+      <c r="O1" s="209"/>
       <c r="P1" s="104"/>
       <c r="Q1" s="104"/>
     </row>
@@ -5574,13 +5644,10 @@
       <c r="J2" s="104"/>
       <c r="K2" s="104"/>
       <c r="L2" s="105" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="M2" s="104"/>
       <c r="N2" s="104"/>
-      <c r="O2" s="106">
-        <v>2818059.97</v>
-      </c>
       <c r="P2" s="106"/>
       <c r="Q2" s="106"/>
       <c r="R2" s="31"/>
@@ -5598,7 +5665,7 @@
       <c r="J3" s="104"/>
       <c r="K3" s="104"/>
       <c r="L3" s="104" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="M3" s="104"/>
       <c r="N3" s="104"/>
@@ -5608,105 +5675,105 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="242" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="231" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="236" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="236" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="240" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="236" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="236" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="236" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="249" t="s">
+      <c r="I4" s="240" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="244" t="s">
+      <c r="J4" s="241" t="s">
         <v>71</v>
       </c>
-      <c r="D4" s="244" t="s">
+      <c r="K4" s="229" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="245" t="s">
+      <c r="L4" s="233" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="244" t="s">
+      <c r="M4" s="229" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="244" t="s">
+      <c r="N4" s="237" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="244" t="s">
+      <c r="O4" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="245" t="s">
+      <c r="P4" s="239" t="s">
         <v>77</v>
       </c>
-      <c r="J4" s="256" t="s">
+      <c r="Q4" s="233" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="248" t="s">
-        <v>79</v>
-      </c>
-      <c r="L4" s="251" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="248" t="s">
-        <v>81</v>
-      </c>
-      <c r="N4" s="253" t="s">
-        <v>82</v>
-      </c>
-      <c r="O4" s="109" t="s">
-        <v>83</v>
-      </c>
-      <c r="P4" s="255" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q4" s="251" t="s">
-        <v>85</v>
-      </c>
       <c r="R4" s="4"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="243"/>
-      <c r="B5" s="250"/>
-      <c r="C5" s="243"/>
-      <c r="D5" s="243"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="243"/>
-      <c r="G5" s="243"/>
-      <c r="H5" s="243"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="243"/>
-      <c r="M5" s="246"/>
-      <c r="N5" s="254"/>
+      <c r="A5" s="234"/>
+      <c r="B5" s="232"/>
+      <c r="C5" s="234"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="230"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="234"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="230"/>
+      <c r="K5" s="230"/>
+      <c r="L5" s="234"/>
+      <c r="M5" s="230"/>
+      <c r="N5" s="238"/>
       <c r="O5" s="110" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="P5" s="250"/>
-      <c r="Q5" s="243"/>
+      <c r="P5" s="232"/>
+      <c r="Q5" s="234"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B6" s="134">
         <v>1</v>
       </c>
       <c r="C6" s="135" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D6" s="135" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E6" s="111" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F6" s="112">
         <v>1.1000000000000001</v>
       </c>
       <c r="G6" s="113">
-        <v>27798.01</v>
+        <v>30999.01</v>
       </c>
       <c r="H6" s="158">
         <f>G6</f>
-        <v>27798.01</v>
+        <v>30999.01</v>
       </c>
       <c r="I6" s="115"/>
       <c r="J6" s="116">
@@ -5722,23 +5789,23 @@
         <v>0</v>
       </c>
       <c r="M6" s="116">
-        <f t="shared" ref="M6:M34" si="3">O$2*F6%</f>
-        <v>30998.659670000005</v>
+        <f>RESUMEN!H$92*F6%</f>
+        <v>0</v>
       </c>
       <c r="N6" s="117">
         <v>0</v>
       </c>
       <c r="O6" s="142">
-        <f t="shared" ref="O6:O34" si="4">ROUND(SUM(J6:N6),0) + R6</f>
-        <v>30999.01</v>
+        <f t="shared" ref="O6:O34" si="3">ROUND(SUM(J6:N6),0) + R6</f>
+        <v>0.01</v>
       </c>
       <c r="P6" s="122">
-        <f t="shared" ref="P6:P36" si="5">ROUND(O6*6% + O6,0) + R6</f>
-        <v>32859.01</v>
+        <f t="shared" ref="P6:P36" si="4">ROUND(O6*6% + O6,0) + R6</f>
+        <v>0.01</v>
       </c>
       <c r="Q6" s="143">
-        <f t="shared" ref="Q6:Q36" si="6">ROUND(O6*3%,0) + O6</f>
-        <v>31929.01</v>
+        <f t="shared" ref="Q6:Q36" si="5">ROUND(O6*3%,0) + O6</f>
+        <v>0.01</v>
       </c>
       <c r="R6" s="74">
         <v>0.01</v>
@@ -5746,146 +5813,152 @@
     </row>
     <row r="7" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="212">
+        <v>83</v>
+      </c>
+      <c r="B7" s="199">
         <v>2</v>
       </c>
-      <c r="C7" s="213" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="213" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="214"/>
-      <c r="F7" s="215">
+      <c r="C7" s="200" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="200" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="201"/>
+      <c r="F7" s="202">
         <v>0.9</v>
       </c>
       <c r="G7" s="166">
-        <v>22744.02</v>
-      </c>
-      <c r="H7" s="158"/>
+        <v>48789.02</v>
+      </c>
+      <c r="H7" s="158">
+        <f>G7</f>
+        <v>48789.02</v>
+      </c>
       <c r="I7" s="115"/>
       <c r="J7" s="167">
         <f t="shared" si="0"/>
-        <v>22744.02</v>
+        <v>0</v>
       </c>
       <c r="K7" s="167">
         <f t="shared" si="1"/>
-        <v>682.32060000000001</v>
+        <v>0</v>
       </c>
       <c r="L7" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M7" s="167">
+        <f>RESUMEN!H$92*F7%</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="168">
+        <v>0</v>
+      </c>
+      <c r="O7" s="169">
         <f t="shared" si="3"/>
-        <v>25362.539730000004</v>
-      </c>
-      <c r="N7" s="168">
-        <v>0</v>
-      </c>
-      <c r="O7" s="169">
+        <v>0.02</v>
+      </c>
+      <c r="P7" s="170">
         <f t="shared" si="4"/>
-        <v>48789.02</v>
-      </c>
-      <c r="P7" s="170">
+        <v>0.02</v>
+      </c>
+      <c r="Q7" s="171">
         <f t="shared" si="5"/>
-        <v>51716.02</v>
-      </c>
-      <c r="Q7" s="171">
-        <f t="shared" si="6"/>
-        <v>50253.02</v>
+        <v>0.02</v>
       </c>
       <c r="R7" s="74">
-        <f t="shared" ref="R7:R35" si="7">R6+0.01</f>
+        <f t="shared" ref="R7:R35" si="6">R6+0.01</f>
         <v>0.02</v>
       </c>
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="212">
+        <v>83</v>
+      </c>
+      <c r="B8" s="199">
         <v>3</v>
       </c>
-      <c r="C8" s="213" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="213" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="214" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="215">
+      <c r="C8" s="200" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="200" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="201" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="202">
         <v>0.8</v>
       </c>
       <c r="G8" s="166">
-        <v>20217.03</v>
-      </c>
-      <c r="H8" s="158"/>
+        <v>43368.03</v>
+      </c>
+      <c r="H8" s="158">
+        <f>G8</f>
+        <v>43368.03</v>
+      </c>
       <c r="I8" s="115"/>
       <c r="J8" s="167">
         <f t="shared" si="0"/>
-        <v>20217.03</v>
+        <v>0</v>
       </c>
       <c r="K8" s="167">
         <f t="shared" si="1"/>
-        <v>606.51089999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M8" s="167">
+        <f>RESUMEN!H$92*F8%</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="168">
+        <v>0</v>
+      </c>
+      <c r="O8" s="169">
         <f t="shared" si="3"/>
-        <v>22544.479760000002</v>
-      </c>
-      <c r="N8" s="168">
-        <v>0</v>
-      </c>
-      <c r="O8" s="169">
+        <v>0.03</v>
+      </c>
+      <c r="P8" s="170">
         <f t="shared" si="4"/>
-        <v>43368.03</v>
-      </c>
-      <c r="P8" s="170">
+        <v>0.03</v>
+      </c>
+      <c r="Q8" s="171">
         <f t="shared" si="5"/>
-        <v>45970.03</v>
-      </c>
-      <c r="Q8" s="171">
+        <v>0.03</v>
+      </c>
+      <c r="R8" s="74">
         <f t="shared" si="6"/>
-        <v>44669.03</v>
-      </c>
-      <c r="R8" s="74">
-        <f t="shared" si="7"/>
         <v>0.03</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="212">
+        <v>89</v>
+      </c>
+      <c r="B9" s="199">
         <v>4</v>
       </c>
-      <c r="C9" s="213" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" s="213" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="214"/>
-      <c r="F9" s="215">
+      <c r="C9" s="200" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="200" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="201"/>
+      <c r="F9" s="202">
         <v>0.8</v>
       </c>
       <c r="G9" s="166">
-        <v>20217.04</v>
+        <v>22544.04</v>
       </c>
       <c r="H9" s="158">
         <f>G9</f>
-        <v>20217.04</v>
+        <v>22544.04</v>
       </c>
       <c r="I9" s="115"/>
       <c r="J9" s="167">
@@ -5901,602 +5974,610 @@
         <v>0</v>
       </c>
       <c r="M9" s="167">
+        <f>RESUMEN!H$92*F9%</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="168">
+        <v>0</v>
+      </c>
+      <c r="O9" s="169">
         <f t="shared" si="3"/>
-        <v>22544.479760000002</v>
-      </c>
-      <c r="N9" s="168">
-        <v>0</v>
-      </c>
-      <c r="O9" s="169">
+        <v>0.04</v>
+      </c>
+      <c r="P9" s="170">
         <f t="shared" si="4"/>
-        <v>22544.04</v>
-      </c>
-      <c r="P9" s="170">
+        <v>0.04</v>
+      </c>
+      <c r="Q9" s="171">
         <f t="shared" si="5"/>
-        <v>23897.040000000001</v>
-      </c>
-      <c r="Q9" s="171">
+        <v>0.04</v>
+      </c>
+      <c r="R9" s="74">
         <f t="shared" si="6"/>
-        <v>23220.04</v>
-      </c>
-      <c r="R9" s="74">
-        <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="212">
+        <v>89</v>
+      </c>
+      <c r="B10" s="199">
         <v>5</v>
       </c>
-      <c r="C10" s="213" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" s="213" t="s">
+      <c r="C10" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="214" t="s">
-        <v>100</v>
-      </c>
-      <c r="F10" s="215">
+      <c r="D10" s="200" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="201" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="202">
         <v>0.5</v>
       </c>
       <c r="G10" s="166">
-        <v>51686.05</v>
+        <v>67327.05</v>
       </c>
       <c r="H10" s="158"/>
       <c r="I10" s="115"/>
       <c r="J10" s="167">
         <f t="shared" si="0"/>
-        <v>51686.05</v>
+        <v>67327.05</v>
       </c>
       <c r="K10" s="167">
         <f t="shared" si="1"/>
-        <v>1550.5815</v>
+        <v>2019.8115</v>
       </c>
       <c r="L10" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M10" s="167">
+        <f>RESUMEN!H$92*F10%</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="168">
+        <v>0</v>
+      </c>
+      <c r="O10" s="169">
         <f t="shared" si="3"/>
-        <v>14090.299850000001</v>
-      </c>
-      <c r="N10" s="168">
-        <v>0</v>
-      </c>
-      <c r="O10" s="169">
+        <v>69347.05</v>
+      </c>
+      <c r="P10" s="170">
         <f t="shared" si="4"/>
-        <v>67327.05</v>
-      </c>
-      <c r="P10" s="170">
+        <v>73508.05</v>
+      </c>
+      <c r="Q10" s="171">
         <f t="shared" si="5"/>
-        <v>71367.05</v>
-      </c>
-      <c r="Q10" s="171">
+        <v>71427.05</v>
+      </c>
+      <c r="R10" s="74">
         <f t="shared" si="6"/>
-        <v>69347.05</v>
-      </c>
-      <c r="R10" s="74">
-        <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="212">
+        <v>94</v>
+      </c>
+      <c r="B11" s="199">
         <v>6</v>
       </c>
-      <c r="C11" s="213" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="213" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="216"/>
-      <c r="F11" s="215">
+      <c r="C11" s="200" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="200" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="203"/>
+      <c r="F11" s="202">
         <v>0.5</v>
       </c>
       <c r="G11" s="166">
-        <v>12635.06</v>
-      </c>
-      <c r="H11" s="158"/>
+        <v>27104.06</v>
+      </c>
+      <c r="H11" s="158">
+        <f>G11</f>
+        <v>27104.06</v>
+      </c>
       <c r="I11" s="115"/>
       <c r="J11" s="167">
         <f t="shared" si="0"/>
-        <v>12635.06</v>
+        <v>0</v>
       </c>
       <c r="K11" s="167">
         <f t="shared" si="1"/>
-        <v>379.05179999999996</v>
+        <v>0</v>
       </c>
       <c r="L11" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M11" s="167">
+        <f>RESUMEN!H$92*F11%</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="168">
+        <v>0</v>
+      </c>
+      <c r="O11" s="169">
         <f t="shared" si="3"/>
-        <v>14090.299850000001</v>
-      </c>
-      <c r="N11" s="168">
-        <v>0</v>
-      </c>
-      <c r="O11" s="169">
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="P11" s="170">
         <f t="shared" si="4"/>
-        <v>27104.06</v>
-      </c>
-      <c r="P11" s="170">
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="Q11" s="171">
         <f t="shared" si="5"/>
-        <v>28730.06</v>
-      </c>
-      <c r="Q11" s="171">
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="R11" s="74">
         <f t="shared" si="6"/>
-        <v>27917.06</v>
-      </c>
-      <c r="R11" s="74">
-        <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="212">
+        <v>94</v>
+      </c>
+      <c r="B12" s="199">
         <v>7</v>
       </c>
-      <c r="C12" s="213" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="213" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="214" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" s="215">
+      <c r="C12" s="200" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="200" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="201" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="202">
         <v>0.5</v>
       </c>
       <c r="G12" s="166">
-        <v>12635.07</v>
-      </c>
-      <c r="H12" s="158"/>
+        <v>27104.07</v>
+      </c>
+      <c r="H12" s="158">
+        <f>G12</f>
+        <v>27104.07</v>
+      </c>
       <c r="I12" s="115"/>
       <c r="J12" s="167">
         <f t="shared" si="0"/>
-        <v>12635.07</v>
+        <v>0</v>
       </c>
       <c r="K12" s="167">
         <f t="shared" si="1"/>
-        <v>379.0521</v>
+        <v>0</v>
       </c>
       <c r="L12" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M12" s="167">
+        <f>RESUMEN!H$92*F12%</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="168">
+        <v>0</v>
+      </c>
+      <c r="O12" s="169">
         <f t="shared" si="3"/>
-        <v>14090.299850000001</v>
-      </c>
-      <c r="N12" s="168">
-        <v>0</v>
-      </c>
-      <c r="O12" s="169">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="P12" s="170">
         <f t="shared" si="4"/>
-        <v>27104.07</v>
-      </c>
-      <c r="P12" s="170">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="Q12" s="171">
         <f t="shared" si="5"/>
-        <v>28730.07</v>
-      </c>
-      <c r="Q12" s="171">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R12" s="74">
         <f t="shared" si="6"/>
-        <v>27917.07</v>
-      </c>
-      <c r="R12" s="74">
-        <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="134" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="135">
+        <v>98</v>
+      </c>
+      <c r="B13" s="251" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="252">
         <v>1</v>
       </c>
-      <c r="D13" s="135" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" s="120" t="s">
-        <v>108</v>
-      </c>
-      <c r="F13" s="112">
+      <c r="D13" s="252" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="253" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="254">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G13" s="113">
-        <v>595422.07999999996</v>
-      </c>
-      <c r="H13" s="158"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="116">
+      <c r="G13" s="255">
+        <v>737279.08</v>
+      </c>
+      <c r="H13" s="256"/>
+      <c r="I13" s="257"/>
+      <c r="J13" s="258">
         <f t="shared" si="0"/>
-        <v>595422.07999999996</v>
-      </c>
-      <c r="K13" s="116">
+        <v>737279.08</v>
+      </c>
+      <c r="K13" s="258">
         <f t="shared" si="1"/>
-        <v>17862.662399999997</v>
-      </c>
-      <c r="L13" s="113">
+        <v>22118.372399999997</v>
+      </c>
+      <c r="L13" s="255">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M13" s="116">
+      <c r="M13" s="258">
+        <f>RESUMEN!H$92*F13%</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="259">
+        <v>0</v>
+      </c>
+      <c r="O13" s="260">
         <f t="shared" si="3"/>
-        <v>123994.63868000002</v>
-      </c>
-      <c r="N13" s="117">
-        <v>0</v>
-      </c>
-      <c r="O13" s="142">
+        <v>759397.08</v>
+      </c>
+      <c r="P13" s="261">
         <f t="shared" si="4"/>
-        <v>737279.08</v>
-      </c>
-      <c r="P13" s="122">
+        <v>804961.08</v>
+      </c>
+      <c r="Q13" s="262">
         <f t="shared" si="5"/>
-        <v>781516.08</v>
-      </c>
-      <c r="Q13" s="143">
+        <v>782179.08</v>
+      </c>
+      <c r="R13" s="74">
         <f t="shared" si="6"/>
-        <v>759397.08</v>
-      </c>
-      <c r="R13" s="74">
-        <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B14" s="134" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C14" s="135">
-        <f t="shared" ref="C14:C34" si="8">C13+1</f>
+        <f t="shared" ref="C14:C34" si="7">C13+1</f>
         <v>2</v>
       </c>
       <c r="D14" s="135" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E14" s="120"/>
       <c r="F14" s="112">
         <v>4.5</v>
       </c>
       <c r="G14" s="113">
-        <v>113716.09</v>
+        <v>126807.09</v>
       </c>
       <c r="H14" s="158">
-        <f>133939-H9</f>
-        <v>113721.95999999999</v>
+        <f>149351-H9</f>
+        <v>126806.95999999999</v>
       </c>
       <c r="I14" s="115"/>
       <c r="J14" s="116">
         <f t="shared" si="0"/>
-        <v>-5.8699999999953434</v>
+        <v>0.13000000000465661</v>
       </c>
       <c r="K14" s="116">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.9000000001396984E-3</v>
       </c>
       <c r="L14" s="113">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M14" s="116">
+        <f>RESUMEN!H$92*F14%</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="117">
+        <v>0</v>
+      </c>
+      <c r="O14" s="142">
         <f t="shared" si="3"/>
-        <v>126812.69865000001</v>
-      </c>
-      <c r="N14" s="117">
-        <v>0</v>
-      </c>
-      <c r="O14" s="142">
+        <v>0.09</v>
+      </c>
+      <c r="P14" s="122">
         <f t="shared" si="4"/>
-        <v>126807.09</v>
-      </c>
-      <c r="P14" s="122">
+        <v>0.09</v>
+      </c>
+      <c r="Q14" s="143">
         <f t="shared" si="5"/>
-        <v>134416.09</v>
-      </c>
-      <c r="Q14" s="143">
+        <v>0.09</v>
+      </c>
+      <c r="R14" s="74">
         <f t="shared" si="6"/>
-        <v>130611.09</v>
-      </c>
-      <c r="R14" s="74">
-        <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
       <c r="U14" s="175" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B15" s="134" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C15" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="D15" s="135" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E15" s="120" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F15" s="112">
         <v>4.5</v>
       </c>
       <c r="G15" s="113">
-        <v>113705</v>
-      </c>
-      <c r="H15" s="209">
-        <v>113705</v>
+        <v>130617.1</v>
+      </c>
+      <c r="H15" s="196">
+        <v>126813</v>
       </c>
       <c r="I15" s="115"/>
       <c r="J15" s="116">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3804.1000000000058</v>
       </c>
       <c r="K15" s="116">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>114.12300000000018</v>
       </c>
       <c r="L15" s="113">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M15" s="116">
+        <f>RESUMEN!H$92*F15%</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="117">
+        <v>0</v>
+      </c>
+      <c r="O15" s="142">
         <f t="shared" si="3"/>
-        <v>126812.69865000001</v>
-      </c>
-      <c r="N15" s="117">
-        <v>0</v>
-      </c>
-      <c r="O15" s="142">
+        <v>3918.1</v>
+      </c>
+      <c r="P15" s="122">
         <f t="shared" si="4"/>
-        <v>126813.1</v>
-      </c>
-      <c r="P15" s="122">
+        <v>4153.1000000000004</v>
+      </c>
+      <c r="Q15" s="143">
         <f t="shared" si="5"/>
-        <v>134422.1</v>
-      </c>
-      <c r="Q15" s="143">
+        <v>4036.1</v>
+      </c>
+      <c r="R15" s="74">
         <f t="shared" si="6"/>
-        <v>130617.1</v>
-      </c>
-      <c r="R15" s="74">
-        <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B16" s="134" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C16" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="D16" s="135" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E16" s="120" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F16" s="112">
         <v>3.1</v>
       </c>
       <c r="G16" s="113">
-        <v>78340.11</v>
+        <v>168050.11</v>
       </c>
       <c r="H16" s="158"/>
       <c r="I16" s="115"/>
       <c r="J16" s="116">
         <f t="shared" si="0"/>
-        <v>78340.11</v>
+        <v>168050.11</v>
       </c>
       <c r="K16" s="116">
         <f t="shared" si="1"/>
-        <v>2350.2033000000001</v>
+        <v>5041.5032999999994</v>
       </c>
       <c r="L16" s="113">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M16" s="116">
+        <f>RESUMEN!H$92*F16%</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="117">
+        <v>0</v>
+      </c>
+      <c r="O16" s="142">
         <f t="shared" si="3"/>
-        <v>87359.859070000006</v>
-      </c>
-      <c r="N16" s="117">
-        <v>0</v>
-      </c>
-      <c r="O16" s="142">
+        <v>173092.11</v>
+      </c>
+      <c r="P16" s="122">
         <f t="shared" si="4"/>
-        <v>168050.11</v>
-      </c>
-      <c r="P16" s="122">
+        <v>183478.11</v>
+      </c>
+      <c r="Q16" s="143">
         <f t="shared" si="5"/>
-        <v>178133.11</v>
-      </c>
-      <c r="Q16" s="143">
+        <v>178285.11</v>
+      </c>
+      <c r="R16" s="74">
         <f t="shared" si="6"/>
-        <v>173092.11</v>
-      </c>
-      <c r="R16" s="74">
-        <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="179" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="180">
-        <f t="shared" si="8"/>
+        <v>111</v>
+      </c>
+      <c r="B17" s="251" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="252">
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="D17" s="180" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" s="181" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="182">
+      <c r="D17" s="252" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="253" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="254">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G17" s="183">
-        <v>454831.12</v>
-      </c>
-      <c r="H17" s="208"/>
-      <c r="I17" s="184"/>
-      <c r="J17" s="185">
+      <c r="G17" s="255">
+        <v>592471.12</v>
+      </c>
+      <c r="H17" s="256">
+        <v>240000</v>
+      </c>
+      <c r="I17" s="257"/>
+      <c r="J17" s="258">
         <f t="shared" si="0"/>
-        <v>454831.12</v>
-      </c>
-      <c r="K17" s="185">
+        <v>352471.12</v>
+      </c>
+      <c r="K17" s="258">
         <f t="shared" si="1"/>
-        <v>13644.933599999998</v>
-      </c>
-      <c r="L17" s="183">
+        <v>10574.133599999999</v>
+      </c>
+      <c r="L17" s="255">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M17" s="185">
+      <c r="M17" s="258">
+        <f>RESUMEN!H$92*F17%</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="259">
+        <v>0</v>
+      </c>
+      <c r="O17" s="260">
         <f t="shared" si="3"/>
-        <v>123994.63868000002</v>
-      </c>
-      <c r="N17" s="186">
-        <v>0</v>
-      </c>
-      <c r="O17" s="187">
+        <v>363045.12</v>
+      </c>
+      <c r="P17" s="261">
         <f t="shared" si="4"/>
-        <v>592471.12</v>
-      </c>
-      <c r="P17" s="188">
+        <v>384828.12</v>
+      </c>
+      <c r="Q17" s="262">
         <f t="shared" si="5"/>
-        <v>628019.12</v>
-      </c>
-      <c r="Q17" s="189">
+        <v>373936.12</v>
+      </c>
+      <c r="R17" s="74">
         <f t="shared" si="6"/>
-        <v>610245.12</v>
-      </c>
-      <c r="R17" s="74">
-        <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" s="134" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="135">
-        <f t="shared" si="8"/>
+        <v>111</v>
+      </c>
+      <c r="B18" s="251" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="252">
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="D18" s="135" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" s="120" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="112">
+      <c r="D18" s="252" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="253" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="254">
         <v>4.5</v>
       </c>
-      <c r="G18" s="113">
-        <v>113719.13</v>
-      </c>
-      <c r="H18" s="158"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="116">
+      <c r="G18" s="255">
+        <v>243943.13</v>
+      </c>
+      <c r="H18" s="256"/>
+      <c r="I18" s="257"/>
+      <c r="J18" s="258">
         <f t="shared" si="0"/>
-        <v>113719.13</v>
-      </c>
-      <c r="K18" s="116">
+        <v>243943.13</v>
+      </c>
+      <c r="K18" s="258">
         <f t="shared" si="1"/>
-        <v>3411.5738999999999</v>
-      </c>
-      <c r="L18" s="113">
+        <v>7318.2938999999997</v>
+      </c>
+      <c r="L18" s="255">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M18" s="116">
+      <c r="M18" s="258">
+        <f>RESUMEN!H$92*F18%</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="259">
+        <v>0</v>
+      </c>
+      <c r="O18" s="260">
         <f t="shared" si="3"/>
-        <v>126812.69865000001</v>
-      </c>
-      <c r="N18" s="117">
-        <v>0</v>
-      </c>
-      <c r="O18" s="142">
+        <v>251261.13</v>
+      </c>
+      <c r="P18" s="261">
         <f t="shared" si="4"/>
-        <v>243943.13</v>
-      </c>
-      <c r="P18" s="122">
+        <v>266337.13</v>
+      </c>
+      <c r="Q18" s="262">
         <f t="shared" si="5"/>
-        <v>258580.13</v>
-      </c>
-      <c r="Q18" s="143">
+        <v>258799.13</v>
+      </c>
+      <c r="R18" s="74">
         <f t="shared" si="6"/>
-        <v>251261.13</v>
-      </c>
-      <c r="R18" s="74">
-        <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B19" s="134" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C19" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="D19" s="135" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E19" s="120"/>
       <c r="F19" s="112">
         <v>4.5</v>
       </c>
       <c r="G19" s="113">
-        <v>113719.14</v>
+        <v>126813.14</v>
       </c>
       <c r="H19" s="158">
         <f>G19</f>
-        <v>113719.14</v>
+        <v>126813.14</v>
       </c>
       <c r="I19" s="115"/>
       <c r="J19" s="116">
@@ -6512,53 +6593,53 @@
         <v>0</v>
       </c>
       <c r="M19" s="116">
+        <f>RESUMEN!H$92*F19%</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="117">
+        <v>0</v>
+      </c>
+      <c r="O19" s="142">
         <f t="shared" si="3"/>
-        <v>126812.69865000001</v>
-      </c>
-      <c r="N19" s="117">
-        <v>0</v>
-      </c>
-      <c r="O19" s="142">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="P19" s="122">
         <f t="shared" si="4"/>
-        <v>126813.14</v>
-      </c>
-      <c r="P19" s="122">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="Q19" s="143">
         <f t="shared" si="5"/>
-        <v>134422.14000000001</v>
-      </c>
-      <c r="Q19" s="143">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R19" s="74">
         <f t="shared" si="6"/>
-        <v>130617.14</v>
-      </c>
-      <c r="R19" s="74">
-        <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B20" s="134" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C20" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="D20" s="135" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E20" s="120"/>
       <c r="F20" s="112">
         <v>3.1</v>
       </c>
       <c r="G20" s="113">
-        <v>78340.149999999994</v>
+        <v>87360.15</v>
       </c>
       <c r="H20" s="158">
         <f>G20</f>
-        <v>78340.149999999994</v>
+        <v>87360.15</v>
       </c>
       <c r="I20" s="115"/>
       <c r="J20" s="116">
@@ -6574,55 +6655,55 @@
         <v>0</v>
       </c>
       <c r="M20" s="116">
+        <f>RESUMEN!H$92*F20%</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="117">
+        <v>0</v>
+      </c>
+      <c r="O20" s="142">
         <f t="shared" si="3"/>
-        <v>87359.859070000006</v>
-      </c>
-      <c r="N20" s="117">
-        <v>0</v>
-      </c>
-      <c r="O20" s="142">
+        <v>0.15</v>
+      </c>
+      <c r="P20" s="122">
         <f t="shared" si="4"/>
-        <v>87360.15</v>
-      </c>
-      <c r="P20" s="122">
+        <v>0.15</v>
+      </c>
+      <c r="Q20" s="143">
         <f t="shared" si="5"/>
-        <v>92602.15</v>
-      </c>
-      <c r="Q20" s="143">
+        <v>0.15</v>
+      </c>
+      <c r="R20" s="74">
         <f t="shared" si="6"/>
-        <v>89981.15</v>
-      </c>
-      <c r="R20" s="74">
-        <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B21" s="134" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C21" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="D21" s="135" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E21" s="111" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F21" s="112">
         <v>4.4000000000000004</v>
       </c>
       <c r="G21" s="113">
-        <v>111192.16</v>
+        <v>123995.16</v>
       </c>
       <c r="H21" s="158">
         <f>G21</f>
-        <v>111192.16</v>
+        <v>123995.16</v>
       </c>
       <c r="I21" s="115"/>
       <c r="J21" s="116">
@@ -6638,121 +6719,121 @@
         <v>0</v>
       </c>
       <c r="M21" s="116">
+        <f>RESUMEN!H$92*F21%</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="117">
+        <v>0</v>
+      </c>
+      <c r="O21" s="142">
         <f t="shared" si="3"/>
-        <v>123994.63868000002</v>
-      </c>
-      <c r="N21" s="117">
-        <v>0</v>
-      </c>
-      <c r="O21" s="142">
+        <v>0.16</v>
+      </c>
+      <c r="P21" s="122">
         <f t="shared" si="4"/>
-        <v>123995.16</v>
-      </c>
-      <c r="P21" s="122">
+        <v>0.16</v>
+      </c>
+      <c r="Q21" s="143">
         <f t="shared" si="5"/>
-        <v>131435.16</v>
-      </c>
-      <c r="Q21" s="143">
+        <v>0.16</v>
+      </c>
+      <c r="R21" s="74">
         <f t="shared" si="6"/>
-        <v>127715.16</v>
-      </c>
-      <c r="R21" s="74">
-        <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
       <c r="T21" s="121"/>
     </row>
     <row r="22" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B22" s="134" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C22" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="D22" s="135" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E22" s="120" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F22" s="112">
         <v>4.5</v>
       </c>
       <c r="G22" s="114">
-        <v>230850.17</v>
+        <v>247458.17</v>
       </c>
       <c r="H22" s="158">
-        <v>113719</v>
+        <v>126813</v>
       </c>
       <c r="I22" s="115"/>
       <c r="J22" s="116">
         <f t="shared" si="0"/>
-        <v>117131.17000000001</v>
+        <v>120645.17000000001</v>
       </c>
       <c r="K22" s="116">
         <f t="shared" si="1"/>
-        <v>3513.9351000000001</v>
+        <v>3619.3551000000002</v>
       </c>
       <c r="L22" s="113">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M22" s="116">
+        <f>RESUMEN!H$92*F22%</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="117">
+        <v>0</v>
+      </c>
+      <c r="O22" s="142">
         <f t="shared" si="3"/>
-        <v>126812.69865000001</v>
-      </c>
-      <c r="N22" s="117">
-        <v>0</v>
-      </c>
-      <c r="O22" s="142">
+        <v>124265.17</v>
+      </c>
+      <c r="P22" s="122">
         <f t="shared" si="4"/>
-        <v>247458.17</v>
-      </c>
-      <c r="P22" s="122">
+        <v>131721.17000000001</v>
+      </c>
+      <c r="Q22" s="143">
         <f t="shared" si="5"/>
-        <v>262306.17</v>
-      </c>
-      <c r="Q22" s="143">
+        <v>127993.17</v>
+      </c>
+      <c r="R22" s="74">
         <f t="shared" si="6"/>
-        <v>254882.17</v>
-      </c>
-      <c r="R22" s="74">
-        <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
       <c r="T22" s="174"/>
-      <c r="U22" s="217" t="s">
-        <v>136</v>
+      <c r="U22" s="204" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B23" s="134" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C23" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="D23" s="135" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E23" s="111"/>
       <c r="F23" s="112">
         <v>4.5</v>
       </c>
       <c r="G23" s="166">
-        <v>113719.18</v>
+        <v>126813.18</v>
       </c>
       <c r="H23" s="158">
         <f>G23</f>
-        <v>113719.18</v>
+        <v>126813.18</v>
       </c>
       <c r="I23" s="115"/>
       <c r="J23" s="167">
@@ -6768,182 +6849,185 @@
         <v>0</v>
       </c>
       <c r="M23" s="167">
+        <f>RESUMEN!H$92*F23%</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="168">
+        <v>0</v>
+      </c>
+      <c r="O23" s="169">
         <f t="shared" si="3"/>
-        <v>126812.69865000001</v>
-      </c>
-      <c r="N23" s="168">
-        <v>0</v>
-      </c>
-      <c r="O23" s="169">
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="P23" s="170">
         <f t="shared" si="4"/>
-        <v>126813.18</v>
-      </c>
-      <c r="P23" s="170">
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="Q23" s="171">
         <f t="shared" si="5"/>
-        <v>134422.18</v>
-      </c>
-      <c r="Q23" s="171">
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="R23" s="74">
         <f t="shared" si="6"/>
-        <v>130617.18</v>
-      </c>
-      <c r="R23" s="74">
-        <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
       <c r="T23" s="174"/>
     </row>
     <row r="24" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B24" s="134" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C24" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="D24" s="135" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E24" s="120" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F24" s="112">
         <v>3.1</v>
       </c>
       <c r="G24" s="113">
-        <v>78340.19</v>
-      </c>
-      <c r="H24" s="158"/>
+        <v>168050.19</v>
+      </c>
+      <c r="H24" s="158">
+        <f>211418-H8</f>
+        <v>168049.97</v>
+      </c>
       <c r="I24" s="115"/>
       <c r="J24" s="116">
         <f t="shared" si="0"/>
-        <v>78340.19</v>
+        <v>0.22000000000116415</v>
       </c>
       <c r="K24" s="116">
         <f t="shared" si="1"/>
-        <v>2350.2057</v>
+        <v>6.6000000000349243E-3</v>
       </c>
       <c r="L24" s="113">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M24" s="116">
+        <f>RESUMEN!H$92*F24%</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="117">
+        <v>0</v>
+      </c>
+      <c r="O24" s="142">
         <f t="shared" si="3"/>
-        <v>87359.859070000006</v>
-      </c>
-      <c r="N24" s="117">
-        <v>0</v>
-      </c>
-      <c r="O24" s="142">
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="P24" s="122">
         <f t="shared" si="4"/>
-        <v>168050.19</v>
-      </c>
-      <c r="P24" s="122">
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="Q24" s="143">
         <f t="shared" si="5"/>
-        <v>178133.19</v>
-      </c>
-      <c r="Q24" s="143">
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="R24" s="74">
         <f t="shared" si="6"/>
-        <v>173092.19</v>
-      </c>
-      <c r="R24" s="74">
-        <f t="shared" si="7"/>
         <v>0.19000000000000003</v>
       </c>
       <c r="T24" s="174"/>
     </row>
     <row r="25" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="B25" s="212" t="s">
-        <v>142</v>
-      </c>
-      <c r="C25" s="213">
-        <f t="shared" si="8"/>
+        <v>134</v>
+      </c>
+      <c r="B25" s="199" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="200">
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="D25" s="213" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" s="216"/>
-      <c r="F25" s="215">
+      <c r="D25" s="200" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="203"/>
+      <c r="F25" s="202">
         <v>4.4000000000000004</v>
       </c>
       <c r="G25" s="166">
-        <v>155094.20000000001</v>
+        <v>283742.2</v>
       </c>
       <c r="H25" s="158"/>
       <c r="I25" s="115"/>
       <c r="J25" s="115">
         <f t="shared" si="0"/>
-        <v>155094.20000000001</v>
+        <v>283742.2</v>
       </c>
       <c r="K25" s="167">
         <f t="shared" si="1"/>
-        <v>4652.826</v>
+        <v>8512.2659999999996</v>
       </c>
       <c r="L25" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M25" s="167">
+        <f>RESUMEN!H$92*F25%</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="168">
+        <v>0</v>
+      </c>
+      <c r="O25" s="169">
         <f t="shared" si="3"/>
-        <v>123994.63868000002</v>
-      </c>
-      <c r="N25" s="168">
-        <v>0</v>
-      </c>
-      <c r="O25" s="169">
+        <v>292254.2</v>
+      </c>
+      <c r="P25" s="170">
         <f t="shared" si="4"/>
-        <v>283742.2</v>
-      </c>
-      <c r="P25" s="170">
+        <v>309789.2</v>
+      </c>
+      <c r="Q25" s="171">
         <f t="shared" si="5"/>
-        <v>300767.2</v>
-      </c>
-      <c r="Q25" s="171">
+        <v>301022.2</v>
+      </c>
+      <c r="R25" s="74">
         <f t="shared" si="6"/>
-        <v>292254.2</v>
-      </c>
-      <c r="R25" s="74">
-        <f t="shared" si="7"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="T25" s="175" t="s">
-        <v>144</v>
-      </c>
-      <c r="U25" s="211"/>
+        <v>137</v>
+      </c>
+      <c r="U25" s="198"/>
       <c r="V25" s="175"/>
     </row>
     <row r="26" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B26" s="134" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C26" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="D26" s="135" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E26" s="120" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F26" s="112">
         <v>4.5</v>
       </c>
       <c r="G26" s="113">
-        <v>113719.21</v>
+        <v>126813.21</v>
       </c>
       <c r="H26" s="158">
-        <f>141517-H6</f>
-        <v>113718.99</v>
+        <f>157812-H6</f>
+        <v>126812.99</v>
       </c>
       <c r="I26" s="115"/>
       <c r="J26" s="116">
@@ -6959,125 +7043,126 @@
         <v>0</v>
       </c>
       <c r="M26" s="116">
+        <f>RESUMEN!H$92*F26%</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="117">
+        <v>0</v>
+      </c>
+      <c r="O26" s="142">
         <f t="shared" si="3"/>
-        <v>126812.69865000001</v>
-      </c>
-      <c r="N26" s="117">
-        <v>0</v>
-      </c>
-      <c r="O26" s="142">
+        <v>0.21000000000000005</v>
+      </c>
+      <c r="P26" s="122">
         <f t="shared" si="4"/>
-        <v>126813.21</v>
-      </c>
-      <c r="P26" s="122">
+        <v>0.21000000000000005</v>
+      </c>
+      <c r="Q26" s="143">
         <f t="shared" si="5"/>
-        <v>134422.21</v>
-      </c>
-      <c r="Q26" s="143">
+        <v>0.21000000000000005</v>
+      </c>
+      <c r="R26" s="74">
         <f t="shared" si="6"/>
-        <v>130617.21</v>
-      </c>
-      <c r="R26" s="74">
-        <f t="shared" si="7"/>
         <v>0.21000000000000005</v>
       </c>
       <c r="T26" s="174"/>
     </row>
     <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B27" s="134" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C27" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="D27" s="135" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E27" s="120" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F27" s="112">
         <v>4.5</v>
       </c>
       <c r="G27" s="113">
-        <v>113719.22</v>
-      </c>
-      <c r="H27" s="158"/>
+        <v>243943.22</v>
+      </c>
+      <c r="H27" s="158">
+        <f>117131+13014-H12</f>
+        <v>103040.93</v>
+      </c>
       <c r="I27" s="115"/>
       <c r="J27" s="116">
         <f t="shared" si="0"/>
-        <v>113719.22</v>
+        <v>140902.29</v>
       </c>
       <c r="K27" s="116">
         <f t="shared" si="1"/>
-        <v>3411.5765999999999</v>
+        <v>4227.0686999999998</v>
       </c>
       <c r="L27" s="113">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M27" s="116">
+        <f>RESUMEN!H$92*F27%</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="117">
+        <v>0</v>
+      </c>
+      <c r="O27" s="142">
         <f t="shared" si="3"/>
-        <v>126812.69865000001</v>
-      </c>
-      <c r="N27" s="117">
-        <v>0</v>
-      </c>
-      <c r="O27" s="142">
+        <v>145129.22</v>
+      </c>
+      <c r="P27" s="122">
         <f t="shared" si="4"/>
-        <v>243943.22</v>
-      </c>
-      <c r="P27" s="122">
+        <v>153837.22</v>
+      </c>
+      <c r="Q27" s="143">
         <f t="shared" si="5"/>
-        <v>258580.22</v>
-      </c>
-      <c r="Q27" s="143">
+        <v>149483.22</v>
+      </c>
+      <c r="R27" s="74">
         <f t="shared" si="6"/>
-        <v>251261.22</v>
-      </c>
-      <c r="R27" s="74">
-        <f t="shared" si="7"/>
         <v>0.22000000000000006</v>
       </c>
-      <c r="T27" s="221" t="s">
-        <v>152</v>
-      </c>
+      <c r="T27" s="208"/>
     </row>
     <row r="28" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B28" s="134" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C28" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="D28" s="135" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E28" s="120" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F28" s="112">
         <v>3.1</v>
       </c>
       <c r="G28" s="113">
-        <v>78340.23</v>
+        <v>87360.23</v>
       </c>
       <c r="H28" s="158">
-        <f>G28</f>
-        <v>78340.23</v>
+        <f>89981</f>
+        <v>89981</v>
       </c>
       <c r="I28" s="115"/>
       <c r="J28" s="116">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2620.7700000000041</v>
       </c>
       <c r="K28" s="116">
         <f t="shared" si="1"/>
@@ -7088,176 +7173,178 @@
         <v>0</v>
       </c>
       <c r="M28" s="116">
+        <f>RESUMEN!H$92*F28%</f>
+        <v>0</v>
+      </c>
+      <c r="N28" s="117">
+        <v>0</v>
+      </c>
+      <c r="O28" s="142">
         <f t="shared" si="3"/>
-        <v>87359.859070000006</v>
-      </c>
-      <c r="N28" s="117">
-        <v>0</v>
-      </c>
-      <c r="O28" s="142">
+        <v>-2620.77</v>
+      </c>
+      <c r="P28" s="122">
         <f t="shared" si="4"/>
-        <v>87360.23</v>
-      </c>
-      <c r="P28" s="122">
+        <v>-2777.77</v>
+      </c>
+      <c r="Q28" s="143">
         <f t="shared" si="5"/>
-        <v>92602.23</v>
-      </c>
-      <c r="Q28" s="143">
+        <v>-2699.77</v>
+      </c>
+      <c r="R28" s="74">
         <f t="shared" si="6"/>
-        <v>89981.23</v>
-      </c>
-      <c r="R28" s="74">
-        <f t="shared" si="7"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B29" s="134" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C29" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="D29" s="135" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E29" s="120"/>
       <c r="F29" s="112">
         <v>6.8</v>
       </c>
       <c r="G29" s="113">
-        <v>171840.24</v>
-      </c>
-      <c r="H29" s="158"/>
+        <v>368624.24</v>
+      </c>
+      <c r="H29" s="158">
+        <f>207219+231100-H7-H11+6198</f>
+        <v>368623.92</v>
+      </c>
       <c r="I29" s="115"/>
       <c r="J29" s="116">
         <f t="shared" si="0"/>
-        <v>171840.24</v>
+        <v>0.32000000000698492</v>
       </c>
       <c r="K29" s="116">
         <f t="shared" si="1"/>
-        <v>5155.2071999999998</v>
+        <v>9.6000000002095468E-3</v>
       </c>
       <c r="L29" s="113">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M29" s="116">
+        <f>RESUMEN!H$92*F29%</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="117">
+        <v>0</v>
+      </c>
+      <c r="O29" s="142">
         <f t="shared" si="3"/>
-        <v>191628.07796000002</v>
-      </c>
-      <c r="N29" s="117">
-        <v>0</v>
-      </c>
-      <c r="O29" s="142">
+        <v>0.24000000000000007</v>
+      </c>
+      <c r="P29" s="122">
         <f t="shared" si="4"/>
-        <v>368624.24</v>
-      </c>
-      <c r="P29" s="122">
+        <v>0.24000000000000007</v>
+      </c>
+      <c r="Q29" s="143">
         <f t="shared" si="5"/>
-        <v>390742.24</v>
-      </c>
-      <c r="Q29" s="143">
+        <v>0.24000000000000007</v>
+      </c>
+      <c r="R29" s="74">
         <f t="shared" si="6"/>
-        <v>379683.24</v>
-      </c>
-      <c r="R29" s="74">
-        <f t="shared" si="7"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B30" s="212" t="s">
-        <v>159</v>
-      </c>
-      <c r="C30" s="213">
-        <f t="shared" si="8"/>
+        <v>149</v>
+      </c>
+      <c r="B30" s="199" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="200">
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="D30" s="213" t="s">
-        <v>160</v>
-      </c>
-      <c r="E30" s="216"/>
-      <c r="F30" s="215">
+      <c r="D30" s="200" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="203"/>
+      <c r="F30" s="202">
         <v>6.9</v>
       </c>
       <c r="G30" s="166">
-        <v>734543.25</v>
+        <v>462426.25</v>
       </c>
       <c r="H30" s="158">
-        <f>174369+100000+200000</f>
-        <v>474369</v>
+        <v>220000</v>
       </c>
       <c r="I30" s="115"/>
       <c r="J30" s="167">
         <f t="shared" si="0"/>
-        <v>260174.25</v>
+        <v>242426.25</v>
       </c>
       <c r="K30" s="167">
         <f t="shared" si="1"/>
-        <v>7805.2275</v>
+        <v>7272.7874999999995</v>
       </c>
       <c r="L30" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M30" s="167">
+        <f>RESUMEN!H$92*F30%</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="168">
+        <v>0</v>
+      </c>
+      <c r="O30" s="169">
         <f t="shared" si="3"/>
-        <v>194446.13793000003</v>
-      </c>
-      <c r="N30" s="168">
-        <v>0</v>
-      </c>
-      <c r="O30" s="169">
+        <v>249699.25</v>
+      </c>
+      <c r="P30" s="170">
         <f t="shared" si="4"/>
-        <v>462426.25</v>
-      </c>
-      <c r="P30" s="170">
+        <v>264681.25</v>
+      </c>
+      <c r="Q30" s="171">
         <f t="shared" si="5"/>
-        <v>490172.25</v>
-      </c>
-      <c r="Q30" s="171">
+        <v>257190.25</v>
+      </c>
+      <c r="R30" s="74">
         <f t="shared" si="6"/>
-        <v>476299.25</v>
-      </c>
-      <c r="R30" s="74">
-        <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B31" s="134" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C31" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="D31" s="135" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E31" s="111" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F31" s="112">
         <v>4.5</v>
       </c>
       <c r="G31" s="113">
-        <v>113719.26</v>
+        <v>126813.26</v>
       </c>
       <c r="H31" s="158">
         <f>G31</f>
-        <v>113719.26</v>
+        <v>126813.26</v>
       </c>
       <c r="I31" s="115"/>
       <c r="J31" s="116">
@@ -7273,175 +7360,177 @@
         <v>0</v>
       </c>
       <c r="M31" s="116">
+        <f>RESUMEN!H$92*F31%</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="117">
+        <v>0</v>
+      </c>
+      <c r="O31" s="142">
         <f t="shared" si="3"/>
-        <v>126812.69865000001</v>
-      </c>
-      <c r="N31" s="117">
-        <v>0</v>
-      </c>
-      <c r="O31" s="142">
+        <v>0.26000000000000006</v>
+      </c>
+      <c r="P31" s="122">
         <f t="shared" si="4"/>
-        <v>126813.26</v>
-      </c>
-      <c r="P31" s="122">
+        <v>0.26000000000000006</v>
+      </c>
+      <c r="Q31" s="143">
         <f t="shared" si="5"/>
-        <v>134422.26</v>
-      </c>
-      <c r="Q31" s="143">
+        <v>0.26000000000000006</v>
+      </c>
+      <c r="R31" s="74">
         <f t="shared" si="6"/>
-        <v>130617.26</v>
-      </c>
-      <c r="R31" s="74">
-        <f t="shared" si="7"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" s="134" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="135">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="D32" s="135" t="s">
         <v>157</v>
       </c>
-      <c r="B32" s="134" t="s">
-        <v>164</v>
-      </c>
-      <c r="C32" s="135">
-        <f t="shared" si="8"/>
-        <v>20</v>
-      </c>
-      <c r="D32" s="135" t="s">
-        <v>165</v>
-      </c>
       <c r="E32" s="120" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F32" s="112">
         <v>3.1</v>
       </c>
       <c r="G32" s="113">
-        <v>78167.27</v>
-      </c>
-      <c r="H32" s="210"/>
+        <v>167872.27</v>
+      </c>
+      <c r="H32" s="197">
+        <v>87360</v>
+      </c>
       <c r="I32" s="115"/>
       <c r="J32" s="116">
         <f t="shared" si="0"/>
-        <v>78167.27</v>
+        <v>80512.26999999999</v>
       </c>
       <c r="K32" s="116">
         <f t="shared" si="1"/>
-        <v>2345.0181000000002</v>
+        <v>2415.3680999999997</v>
       </c>
       <c r="L32" s="113">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M32" s="116">
+        <f>RESUMEN!H$92*F32%</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="117">
+        <v>0</v>
+      </c>
+      <c r="O32" s="142">
         <f t="shared" si="3"/>
-        <v>87359.859070000006</v>
-      </c>
-      <c r="N32" s="117">
-        <v>0</v>
-      </c>
-      <c r="O32" s="142">
+        <v>82928.27</v>
+      </c>
+      <c r="P32" s="122">
         <f t="shared" si="4"/>
-        <v>167872.27</v>
-      </c>
-      <c r="P32" s="122">
+        <v>87904.27</v>
+      </c>
+      <c r="Q32" s="143">
         <f t="shared" si="5"/>
-        <v>177945.27</v>
-      </c>
-      <c r="Q32" s="143">
+        <v>85416.27</v>
+      </c>
+      <c r="R32" s="74">
         <f t="shared" si="6"/>
-        <v>172908.27</v>
-      </c>
-      <c r="R32" s="74">
-        <f t="shared" si="7"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B33" s="134" t="s">
-        <v>167</v>
-      </c>
-      <c r="C33" s="135">
-        <f t="shared" si="8"/>
+        <v>149</v>
+      </c>
+      <c r="B33" s="251" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="252">
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
-      <c r="D33" s="135" t="s">
-        <v>168</v>
-      </c>
-      <c r="E33" s="111" t="s">
-        <v>169</v>
-      </c>
-      <c r="F33" s="112">
+      <c r="D33" s="252" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" s="263" t="s">
+        <v>161</v>
+      </c>
+      <c r="F33" s="254">
         <v>4.5</v>
       </c>
-      <c r="G33" s="113">
-        <v>392736.28</v>
-      </c>
-      <c r="H33" s="158"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="116">
+      <c r="G33" s="255">
+        <v>573819.28</v>
+      </c>
+      <c r="H33" s="256"/>
+      <c r="I33" s="257"/>
+      <c r="J33" s="258">
         <f t="shared" si="0"/>
-        <v>392736.28</v>
-      </c>
-      <c r="K33" s="116">
+        <v>573819.28</v>
+      </c>
+      <c r="K33" s="258">
         <f t="shared" si="1"/>
-        <v>11782.088400000001</v>
-      </c>
-      <c r="L33" s="113">
+        <v>17214.578399999999</v>
+      </c>
+      <c r="L33" s="255">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M33" s="116">
+      <c r="M33" s="258">
+        <f>RESUMEN!H$92*F33%</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="261">
+        <v>42488</v>
+      </c>
+      <c r="O33" s="260">
         <f t="shared" si="3"/>
-        <v>126812.69865000001</v>
-      </c>
-      <c r="N33" s="122">
-        <v>42488</v>
-      </c>
-      <c r="O33" s="142">
+        <v>633522.28</v>
+      </c>
+      <c r="P33" s="261">
         <f t="shared" si="4"/>
-        <v>573819.28</v>
-      </c>
-      <c r="P33" s="122">
+        <v>671534.28</v>
+      </c>
+      <c r="Q33" s="262">
         <f t="shared" si="5"/>
-        <v>608248.28</v>
-      </c>
-      <c r="Q33" s="143">
+        <v>652528.28</v>
+      </c>
+      <c r="R33" s="74">
         <f t="shared" si="6"/>
-        <v>591034.28</v>
-      </c>
-      <c r="R33" s="74">
-        <f t="shared" si="7"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B34" s="134" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C34" s="135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="D34" s="135" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E34" s="111"/>
       <c r="F34" s="112">
         <v>3.1</v>
       </c>
       <c r="G34" s="113">
-        <v>78340.289999999994</v>
+        <v>87360.29</v>
       </c>
       <c r="H34" s="158">
         <f>G34</f>
-        <v>78340.289999999994</v>
+        <v>87360.29</v>
       </c>
       <c r="I34" s="115"/>
       <c r="J34" s="116">
@@ -7457,32 +7546,32 @@
         <v>0</v>
       </c>
       <c r="M34" s="116">
+        <f>RESUMEN!H$92*F34%</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="117">
+        <v>0</v>
+      </c>
+      <c r="O34" s="142">
         <f t="shared" si="3"/>
-        <v>87359.859070000006</v>
-      </c>
-      <c r="N34" s="117">
-        <v>0</v>
-      </c>
-      <c r="O34" s="142">
+        <v>0.29000000000000009</v>
+      </c>
+      <c r="P34" s="122">
         <f t="shared" si="4"/>
-        <v>87360.29</v>
-      </c>
-      <c r="P34" s="122">
+        <v>0.29000000000000009</v>
+      </c>
+      <c r="Q34" s="143">
         <f t="shared" si="5"/>
-        <v>92602.29</v>
-      </c>
-      <c r="Q34" s="143">
+        <v>0.29000000000000009</v>
+      </c>
+      <c r="R34" s="74">
         <f t="shared" si="6"/>
-        <v>89981.29</v>
-      </c>
-      <c r="R34" s="74">
-        <f t="shared" si="7"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B35" s="136"/>
       <c r="C35" s="136"/>
@@ -7507,21 +7596,21 @@
       </c>
       <c r="O35" s="118"/>
       <c r="P35" s="117">
+        <f t="shared" si="4"/>
+        <v>0.3000000000000001</v>
+      </c>
+      <c r="Q35" s="119">
         <f t="shared" si="5"/>
-        <v>0.3000000000000001</v>
-      </c>
-      <c r="Q35" s="119">
+        <v>0</v>
+      </c>
+      <c r="R35" s="74">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R35" s="74">
-        <f t="shared" si="7"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B36" s="111"/>
       <c r="C36" s="111"/>
@@ -7544,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="125">
-        <f>O$2*F36%</f>
+        <f>RESUMEN!H$92*F36%</f>
         <v>0</v>
       </c>
       <c r="N36" s="126">
@@ -7555,11 +7644,11 @@
         <v>0</v>
       </c>
       <c r="P36" s="117">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="119">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R36" s="74"/>
@@ -7570,52 +7659,52 @@
       <c r="D37" s="129"/>
       <c r="E37" s="129"/>
       <c r="F37" s="137">
-        <f t="shared" ref="F37:Q37" si="9">SUM(F6:F36)</f>
+        <f t="shared" ref="F37:Q37" si="8">SUM(F6:F36)</f>
         <v>99.999999999999986</v>
       </c>
       <c r="G37" s="130">
-        <f t="shared" si="9"/>
-        <v>4394046.25</v>
+        <f t="shared" si="8"/>
+        <v>5675667.3500000006</v>
       </c>
       <c r="H37" s="131">
-        <f t="shared" si="9"/>
-        <v>1664619.4100000001</v>
+        <f t="shared" si="8"/>
+        <v>2663365.1799999997</v>
       </c>
       <c r="I37" s="130">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J37" s="131">
-        <f t="shared" si="9"/>
-        <v>2729426.84</v>
+        <f t="shared" si="8"/>
+        <v>3012302.169999999</v>
       </c>
       <c r="K37" s="130">
-        <f t="shared" si="9"/>
-        <v>81882.981299999985</v>
+        <f t="shared" si="8"/>
+        <v>90447.688199999975</v>
       </c>
       <c r="L37" s="131">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M37" s="130">
-        <f t="shared" si="9"/>
-        <v>2818059.9700000007</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="N37" s="131">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>42488</v>
       </c>
       <c r="O37" s="132">
-        <f t="shared" si="9"/>
-        <v>5671863.3500000006</v>
+        <f t="shared" si="8"/>
+        <v>3145240.3499999996</v>
       </c>
       <c r="P37" s="132">
-        <f t="shared" si="9"/>
-        <v>6012181.6500000004</v>
+        <f t="shared" si="8"/>
+        <v>3333957.6499999994</v>
       </c>
       <c r="Q37" s="132">
-        <f t="shared" si="9"/>
-        <v>5842018.3500000006</v>
+        <f t="shared" si="8"/>
+        <v>3239598.3499999996</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7632,95 +7721,95 @@
       <c r="Q39" s="4"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="247" t="s">
-        <v>172</v>
-      </c>
-      <c r="E40" s="223"/>
-      <c r="F40" s="223"/>
-      <c r="G40" s="223"/>
-      <c r="H40" s="223"/>
-      <c r="I40" s="223"/>
-      <c r="J40" s="223"/>
-      <c r="K40" s="223"/>
-      <c r="L40" s="223"/>
-      <c r="M40" s="223"/>
-      <c r="N40" s="223"/>
-      <c r="O40" s="223"/>
+      <c r="D40" s="228" t="s">
+        <v>164</v>
+      </c>
+      <c r="E40" s="209"/>
+      <c r="F40" s="209"/>
+      <c r="G40" s="209"/>
+      <c r="H40" s="209"/>
+      <c r="I40" s="209"/>
+      <c r="J40" s="209"/>
+      <c r="K40" s="209"/>
+      <c r="L40" s="209"/>
+      <c r="M40" s="209"/>
+      <c r="N40" s="209"/>
+      <c r="O40" s="209"/>
       <c r="Q40" s="4"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="223"/>
-      <c r="E41" s="223"/>
-      <c r="F41" s="223"/>
-      <c r="G41" s="223"/>
-      <c r="H41" s="223"/>
-      <c r="I41" s="223"/>
-      <c r="J41" s="223"/>
-      <c r="K41" s="223"/>
-      <c r="L41" s="223"/>
-      <c r="M41" s="223"/>
-      <c r="N41" s="223"/>
-      <c r="O41" s="223"/>
+      <c r="D41" s="209"/>
+      <c r="E41" s="209"/>
+      <c r="F41" s="209"/>
+      <c r="G41" s="209"/>
+      <c r="H41" s="209"/>
+      <c r="I41" s="209"/>
+      <c r="J41" s="209"/>
+      <c r="K41" s="209"/>
+      <c r="L41" s="209"/>
+      <c r="M41" s="209"/>
+      <c r="N41" s="209"/>
+      <c r="O41" s="209"/>
       <c r="Q41" s="4"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="223"/>
-      <c r="E42" s="223"/>
-      <c r="F42" s="223"/>
-      <c r="G42" s="223"/>
-      <c r="H42" s="223"/>
-      <c r="I42" s="223"/>
-      <c r="J42" s="223"/>
-      <c r="K42" s="223"/>
-      <c r="L42" s="223"/>
-      <c r="M42" s="223"/>
-      <c r="N42" s="223"/>
-      <c r="O42" s="223"/>
+      <c r="D42" s="209"/>
+      <c r="E42" s="209"/>
+      <c r="F42" s="209"/>
+      <c r="G42" s="209"/>
+      <c r="H42" s="209"/>
+      <c r="I42" s="209"/>
+      <c r="J42" s="209"/>
+      <c r="K42" s="209"/>
+      <c r="L42" s="209"/>
+      <c r="M42" s="209"/>
+      <c r="N42" s="209"/>
+      <c r="O42" s="209"/>
       <c r="Q42" s="4"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="223"/>
-      <c r="E43" s="223"/>
-      <c r="F43" s="223"/>
-      <c r="G43" s="223"/>
-      <c r="H43" s="223"/>
-      <c r="I43" s="223"/>
-      <c r="J43" s="223"/>
-      <c r="K43" s="223"/>
-      <c r="L43" s="223"/>
-      <c r="M43" s="223"/>
-      <c r="N43" s="223"/>
-      <c r="O43" s="223"/>
+      <c r="D43" s="209"/>
+      <c r="E43" s="209"/>
+      <c r="F43" s="209"/>
+      <c r="G43" s="209"/>
+      <c r="H43" s="209"/>
+      <c r="I43" s="209"/>
+      <c r="J43" s="209"/>
+      <c r="K43" s="209"/>
+      <c r="L43" s="209"/>
+      <c r="M43" s="209"/>
+      <c r="N43" s="209"/>
+      <c r="O43" s="209"/>
       <c r="Q43" s="4"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="223"/>
-      <c r="E44" s="223"/>
-      <c r="F44" s="223"/>
-      <c r="G44" s="223"/>
-      <c r="H44" s="223"/>
-      <c r="I44" s="223"/>
-      <c r="J44" s="223"/>
-      <c r="K44" s="223"/>
-      <c r="L44" s="223"/>
-      <c r="M44" s="223"/>
-      <c r="N44" s="223"/>
-      <c r="O44" s="223"/>
+      <c r="D44" s="209"/>
+      <c r="E44" s="209"/>
+      <c r="F44" s="209"/>
+      <c r="G44" s="209"/>
+      <c r="H44" s="209"/>
+      <c r="I44" s="209"/>
+      <c r="J44" s="209"/>
+      <c r="K44" s="209"/>
+      <c r="L44" s="209"/>
+      <c r="M44" s="209"/>
+      <c r="N44" s="209"/>
+      <c r="O44" s="209"/>
       <c r="Q44" s="4"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="223"/>
-      <c r="E45" s="223"/>
-      <c r="F45" s="223"/>
-      <c r="G45" s="223"/>
-      <c r="H45" s="223"/>
-      <c r="I45" s="223"/>
-      <c r="J45" s="223"/>
-      <c r="K45" s="223"/>
-      <c r="L45" s="223"/>
-      <c r="M45" s="223"/>
-      <c r="N45" s="223"/>
-      <c r="O45" s="223"/>
+      <c r="D45" s="209"/>
+      <c r="E45" s="209"/>
+      <c r="F45" s="209"/>
+      <c r="G45" s="209"/>
+      <c r="H45" s="209"/>
+      <c r="I45" s="209"/>
+      <c r="J45" s="209"/>
+      <c r="K45" s="209"/>
+      <c r="L45" s="209"/>
+      <c r="M45" s="209"/>
+      <c r="N45" s="209"/>
+      <c r="O45" s="209"/>
       <c r="Q45" s="4"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13191,6 +13280,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="D40:O45"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
@@ -13204,13 +13298,8 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ILLIA/Junio/ILLIA-JUNIO.xlsx
+++ b/ILLIA/Junio/ILLIA-JUNIO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661A9F4F-AF68-438B-8606-9FFDB9F1E0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DD2DB0-620C-470F-A29C-E378D842E1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -828,7 +828,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -941,6 +941,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEE0000"/>
         <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1445,7 +1451,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="29"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="264">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1749,90 +1755,10 @@
     <xf numFmtId="165" fontId="7" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="18" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1863,6 +1789,85 @@
     <xf numFmtId="167" fontId="21" fillId="18" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2118,11 +2123,11 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
-      <c r="B3" s="219" t="s">
+      <c r="B3" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="209"/>
+      <c r="C3" s="230"/>
+      <c r="D3" s="230"/>
       <c r="E3" s="9"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -2130,9 +2135,9 @@
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
-      <c r="B4" s="211"/>
-      <c r="C4" s="211"/>
-      <c r="D4" s="211"/>
+      <c r="B4" s="231"/>
+      <c r="C4" s="231"/>
+      <c r="D4" s="231"/>
       <c r="E4" s="9"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -2170,13 +2175,13 @@
       <c r="I6" s="156"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="210" t="s">
+      <c r="A7" s="244" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="211"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="212"/>
+      <c r="B7" s="231"/>
+      <c r="C7" s="231"/>
+      <c r="D7" s="231"/>
+      <c r="E7" s="245"/>
       <c r="F7" s="17"/>
       <c r="G7" s="157"/>
       <c r="H7" s="157"/>
@@ -2189,10 +2194,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="223" t="s">
+      <c r="B9" s="237" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="209"/>
+      <c r="C9" s="230"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -2201,8 +2206,8 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="209"/>
-      <c r="C10" s="209"/>
+      <c r="B10" s="230"/>
+      <c r="C10" s="230"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -2211,8 +2216,8 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="209"/>
-      <c r="C11" s="209"/>
+      <c r="B11" s="230"/>
+      <c r="C11" s="230"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -2231,43 +2236,43 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="213" t="s">
+      <c r="A14" s="246" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="209"/>
-      <c r="C14" s="209"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="209"/>
+      <c r="B14" s="230"/>
+      <c r="C14" s="230"/>
+      <c r="D14" s="230"/>
+      <c r="E14" s="230"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="209"/>
-      <c r="B15" s="209"/>
-      <c r="C15" s="209"/>
-      <c r="D15" s="209"/>
-      <c r="E15" s="209"/>
+      <c r="A15" s="230"/>
+      <c r="B15" s="230"/>
+      <c r="C15" s="230"/>
+      <c r="D15" s="230"/>
+      <c r="E15" s="230"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="209"/>
-      <c r="B16" s="209"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="209"/>
-      <c r="E16" s="209"/>
+      <c r="A16" s="230"/>
+      <c r="B16" s="230"/>
+      <c r="C16" s="230"/>
+      <c r="D16" s="230"/>
+      <c r="E16" s="230"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="209"/>
-      <c r="B17" s="209"/>
-      <c r="C17" s="209"/>
-      <c r="D17" s="209"/>
-      <c r="E17" s="209"/>
+      <c r="A17" s="230"/>
+      <c r="B17" s="230"/>
+      <c r="C17" s="230"/>
+      <c r="D17" s="230"/>
+      <c r="E17" s="230"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
@@ -2679,11 +2684,11 @@
       <c r="A40" s="140" t="s">
         <v>18</v>
       </c>
-      <c r="B40" s="243" t="s">
+      <c r="B40" s="209" t="s">
         <v>173</v>
       </c>
       <c r="C40" s="25"/>
-      <c r="D40" s="249">
+      <c r="D40" s="213">
         <f>2*28000</f>
         <v>56000</v>
       </c>
@@ -2714,7 +2719,7 @@
       <c r="A41" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B41" s="243" t="s">
+      <c r="B41" s="209" t="s">
         <v>174</v>
       </c>
       <c r="C41" s="25"/>
@@ -2791,10 +2796,10 @@
       <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="227" t="s">
+      <c r="A44" s="242" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="215"/>
+      <c r="B44" s="233"/>
       <c r="C44" s="37"/>
       <c r="D44" s="188">
         <v>56041.08</v>
@@ -2869,7 +2874,7 @@
       </c>
       <c r="F48" s="4"/>
     </row>
-    <row r="49" spans="1:26" s="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" s="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
         <v>178</v>
       </c>
@@ -2881,7 +2886,7 @@
       <c r="E49" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="F49" s="244"/>
+      <c r="F49" s="155"/>
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="25" t="s">
@@ -3005,10 +3010,10 @@
       <c r="Z54" s="4"/>
     </row>
     <row r="55" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="226" t="s">
+      <c r="A55" s="241" t="s">
         <v>168</v>
       </c>
-      <c r="B55" s="215"/>
+      <c r="B55" s="233"/>
       <c r="C55" s="25"/>
       <c r="D55" s="192">
         <v>94000</v>
@@ -3068,8 +3073,8 @@
       <c r="Y56" s="4"/>
       <c r="Z56" s="4"/>
     </row>
-    <row r="57" spans="1:26" s="245" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="248" t="s">
+    <row r="57" spans="1:26" s="156" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="212" t="s">
         <v>184</v>
       </c>
       <c r="B57" s="173"/>
@@ -3080,30 +3085,30 @@
       <c r="E57" s="150" t="s">
         <v>183</v>
       </c>
-      <c r="F57" s="244"/>
-      <c r="G57" s="244"/>
-      <c r="H57" s="244"/>
-      <c r="I57" s="244"/>
-      <c r="J57" s="244"/>
-      <c r="K57" s="244"/>
-      <c r="L57" s="244"/>
-      <c r="M57" s="244"/>
-      <c r="N57" s="244"/>
-      <c r="O57" s="244"/>
-      <c r="P57" s="244"/>
-      <c r="Q57" s="244"/>
-      <c r="R57" s="244"/>
-      <c r="S57" s="244"/>
-      <c r="T57" s="244"/>
-      <c r="U57" s="244"/>
-      <c r="V57" s="244"/>
-      <c r="W57" s="244"/>
-      <c r="X57" s="244"/>
-      <c r="Y57" s="244"/>
-      <c r="Z57" s="244"/>
-    </row>
-    <row r="58" spans="1:26" s="245" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="248" t="s">
+      <c r="F57" s="155"/>
+      <c r="G57" s="155"/>
+      <c r="H57" s="155"/>
+      <c r="I57" s="155"/>
+      <c r="J57" s="155"/>
+      <c r="K57" s="155"/>
+      <c r="L57" s="155"/>
+      <c r="M57" s="155"/>
+      <c r="N57" s="155"/>
+      <c r="O57" s="155"/>
+      <c r="P57" s="155"/>
+      <c r="Q57" s="155"/>
+      <c r="R57" s="155"/>
+      <c r="S57" s="155"/>
+      <c r="T57" s="155"/>
+      <c r="U57" s="155"/>
+      <c r="V57" s="155"/>
+      <c r="W57" s="155"/>
+      <c r="X57" s="155"/>
+      <c r="Y57" s="155"/>
+      <c r="Z57" s="155"/>
+    </row>
+    <row r="58" spans="1:26" s="156" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="212" t="s">
         <v>185</v>
       </c>
       <c r="B58" s="173"/>
@@ -3114,27 +3119,27 @@
       <c r="E58" s="150" t="s">
         <v>183</v>
       </c>
-      <c r="F58" s="244"/>
-      <c r="G58" s="244"/>
-      <c r="H58" s="244"/>
-      <c r="I58" s="244"/>
-      <c r="J58" s="244"/>
-      <c r="K58" s="244"/>
-      <c r="L58" s="244"/>
-      <c r="M58" s="244"/>
-      <c r="N58" s="244"/>
-      <c r="O58" s="244"/>
-      <c r="P58" s="244"/>
-      <c r="Q58" s="244"/>
-      <c r="R58" s="244"/>
-      <c r="S58" s="244"/>
-      <c r="T58" s="244"/>
-      <c r="U58" s="244"/>
-      <c r="V58" s="244"/>
-      <c r="W58" s="244"/>
-      <c r="X58" s="244"/>
-      <c r="Y58" s="244"/>
-      <c r="Z58" s="244"/>
+      <c r="F58" s="155"/>
+      <c r="G58" s="155"/>
+      <c r="H58" s="155"/>
+      <c r="I58" s="155"/>
+      <c r="J58" s="155"/>
+      <c r="K58" s="155"/>
+      <c r="L58" s="155"/>
+      <c r="M58" s="155"/>
+      <c r="N58" s="155"/>
+      <c r="O58" s="155"/>
+      <c r="P58" s="155"/>
+      <c r="Q58" s="155"/>
+      <c r="R58" s="155"/>
+      <c r="S58" s="155"/>
+      <c r="T58" s="155"/>
+      <c r="U58" s="155"/>
+      <c r="V58" s="155"/>
+      <c r="W58" s="155"/>
+      <c r="X58" s="155"/>
+      <c r="Y58" s="155"/>
+      <c r="Z58" s="155"/>
     </row>
     <row r="59" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="139" t="s">
@@ -3142,7 +3147,7 @@
       </c>
       <c r="B59" s="138"/>
       <c r="C59" s="49"/>
-      <c r="D59" s="250">
+      <c r="D59" s="214">
         <v>19588.650000000001</v>
       </c>
       <c r="E59" s="163" t="s">
@@ -3153,10 +3158,10 @@
       <c r="H59" s="50"/>
     </row>
     <row r="60" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="214" t="s">
+      <c r="A60" s="232" t="s">
         <v>34</v>
       </c>
-      <c r="B60" s="215"/>
+      <c r="B60" s="233"/>
       <c r="C60" s="49"/>
       <c r="D60" s="193">
         <v>80080</v>
@@ -3169,10 +3174,10 @@
       <c r="H60" s="50"/>
     </row>
     <row r="61" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="214" t="s">
+      <c r="A61" s="232" t="s">
         <v>169</v>
       </c>
-      <c r="B61" s="215"/>
+      <c r="B61" s="233"/>
       <c r="C61" s="33"/>
       <c r="D61" s="187">
         <v>201284.99</v>
@@ -3203,10 +3208,10 @@
       <c r="Z61" s="4"/>
     </row>
     <row r="62" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="214" t="s">
+      <c r="A62" s="232" t="s">
         <v>35</v>
       </c>
-      <c r="B62" s="215"/>
+      <c r="B62" s="233"/>
       <c r="C62" s="33"/>
       <c r="D62" s="187"/>
       <c r="E62" s="164"/>
@@ -3225,8 +3230,8 @@
       <c r="H63" s="4"/>
     </row>
     <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="226"/>
-      <c r="B64" s="215"/>
+      <c r="A64" s="241"/>
+      <c r="B64" s="233"/>
       <c r="C64" s="25"/>
       <c r="D64" s="188"/>
       <c r="E64" s="48"/>
@@ -3281,11 +3286,11 @@
       <c r="Z65" s="4"/>
     </row>
     <row r="66" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="214"/>
-      <c r="B66" s="220"/>
+      <c r="A66" s="232"/>
+      <c r="B66" s="234"/>
       <c r="C66" s="53"/>
-      <c r="D66" s="225"/>
-      <c r="E66" s="217"/>
+      <c r="D66" s="239"/>
+      <c r="E66" s="247"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
@@ -3309,11 +3314,11 @@
       <c r="Z66" s="4"/>
     </row>
     <row r="67" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="221"/>
-      <c r="B67" s="222"/>
+      <c r="A67" s="235"/>
+      <c r="B67" s="236"/>
       <c r="C67" s="53"/>
-      <c r="D67" s="218"/>
-      <c r="E67" s="218"/>
+      <c r="D67" s="240"/>
+      <c r="E67" s="240"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
@@ -3337,8 +3342,8 @@
       <c r="Z67" s="4"/>
     </row>
     <row r="68" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="214"/>
-      <c r="B68" s="215"/>
+      <c r="A68" s="232"/>
+      <c r="B68" s="233"/>
       <c r="C68" s="25"/>
       <c r="D68" s="194"/>
       <c r="E68" s="54"/>
@@ -3365,8 +3370,8 @@
       <c r="Z68" s="4"/>
     </row>
     <row r="69" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="214"/>
-      <c r="B69" s="215"/>
+      <c r="A69" s="232"/>
+      <c r="B69" s="233"/>
       <c r="C69" s="25"/>
       <c r="D69" s="194"/>
       <c r="E69" s="54"/>
@@ -3393,8 +3398,8 @@
       <c r="Z69" s="4"/>
     </row>
     <row r="70" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="214"/>
-      <c r="B70" s="215"/>
+      <c r="A70" s="232"/>
+      <c r="B70" s="233"/>
       <c r="C70" s="25"/>
       <c r="D70" s="194"/>
       <c r="E70" s="48"/>
@@ -3428,8 +3433,8 @@
       <c r="Z71" s="4"/>
     </row>
     <row r="72" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="214"/>
-      <c r="B72" s="215"/>
+      <c r="A72" s="232"/>
+      <c r="B72" s="233"/>
       <c r="C72" s="25"/>
       <c r="D72" s="194"/>
       <c r="E72" s="48"/>
@@ -3484,8 +3489,8 @@
       <c r="Z73" s="4"/>
     </row>
     <row r="74" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="214"/>
-      <c r="B74" s="215"/>
+      <c r="A74" s="232"/>
+      <c r="B74" s="233"/>
       <c r="C74" s="25"/>
       <c r="D74" s="194"/>
       <c r="E74" s="57"/>
@@ -3512,8 +3517,8 @@
       <c r="Z74" s="4"/>
     </row>
     <row r="75" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="214"/>
-      <c r="B75" s="215"/>
+      <c r="A75" s="232"/>
+      <c r="B75" s="233"/>
       <c r="C75" s="25"/>
       <c r="D75" s="194"/>
       <c r="E75" s="57"/>
@@ -3540,8 +3545,8 @@
       <c r="Z75" s="4"/>
     </row>
     <row r="76" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="216"/>
-      <c r="B76" s="215"/>
+      <c r="A76" s="243"/>
+      <c r="B76" s="233"/>
       <c r="C76" s="58"/>
       <c r="D76" s="194"/>
       <c r="E76" s="57"/>
@@ -3589,8 +3594,8 @@
       <c r="E78" s="59"/>
     </row>
     <row r="79" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="214"/>
-      <c r="B79" s="215"/>
+      <c r="A79" s="232"/>
+      <c r="B79" s="233"/>
       <c r="C79" s="60"/>
       <c r="D79" s="190"/>
       <c r="E79" s="57"/>
@@ -3617,15 +3622,15 @@
       <c r="Z79" s="4"/>
     </row>
     <row r="80" spans="1:26" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="214"/>
-      <c r="B80" s="215"/>
+      <c r="A80" s="232"/>
+      <c r="B80" s="233"/>
       <c r="C80" s="61"/>
       <c r="D80" s="190"/>
       <c r="E80" s="62"/>
     </row>
     <row r="81" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="216"/>
-      <c r="B81" s="215"/>
+      <c r="A81" s="243"/>
+      <c r="B81" s="233"/>
       <c r="C81" s="25"/>
       <c r="D81" s="190"/>
       <c r="E81" s="62"/>
@@ -3828,7 +3833,7 @@
         <v>2818059.9699999997</v>
       </c>
       <c r="F92" s="4"/>
-      <c r="G92" s="264"/>
+      <c r="G92" s="228"/>
       <c r="H92" s="106"/>
     </row>
     <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4318,14 +4323,14 @@
       </c>
       <c r="C115" s="85"/>
     </row>
-    <row r="116" spans="1:26" s="245" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" s="156" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="146" t="s">
         <v>182</v>
       </c>
-      <c r="B116" s="247">
+      <c r="B116" s="211">
         <v>-6918</v>
       </c>
-      <c r="C116" s="246"/>
+      <c r="C116" s="210"/>
     </row>
     <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="87" t="s">
@@ -4586,16 +4591,16 @@
     <row r="132" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="133" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="224" t="s">
+      <c r="A134" s="238" t="s">
         <v>59</v>
       </c>
-      <c r="B134" s="209"/>
-      <c r="C134" s="209"/>
+      <c r="B134" s="230"/>
+      <c r="C134" s="230"/>
     </row>
     <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="209"/>
-      <c r="B135" s="209"/>
-      <c r="C135" s="209"/>
+      <c r="A135" s="230"/>
+      <c r="B135" s="230"/>
+      <c r="C135" s="230"/>
     </row>
     <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="25"/>
@@ -5552,6 +5557,14 @@
     <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="A72:B72"/>
     <mergeCell ref="B3:D4"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A66:B67"/>
@@ -5568,14 +5581,6 @@
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="A72:B72"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5594,13 +5599,13 @@
     <col min="5" max="5" width="11.5703125" customWidth="1"/>
     <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.5703125" customWidth="1"/>
     <col min="11" max="11" width="9.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.42578125" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" customWidth="1"/>
     <col min="16" max="16" width="0.42578125" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="14.28515625" customWidth="1"/>
@@ -5615,16 +5620,16 @@
       <c r="C1" s="104"/>
       <c r="D1" s="104"/>
       <c r="E1" s="104"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="209"/>
-      <c r="H1" s="209"/>
-      <c r="I1" s="209"/>
-      <c r="J1" s="209"/>
-      <c r="K1" s="209"/>
-      <c r="L1" s="209"/>
-      <c r="M1" s="209"/>
-      <c r="N1" s="209"/>
-      <c r="O1" s="209"/>
+      <c r="F1" s="258"/>
+      <c r="G1" s="230"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
+      <c r="K1" s="230"/>
+      <c r="L1" s="230"/>
+      <c r="M1" s="230"/>
+      <c r="N1" s="230"/>
+      <c r="O1" s="230"/>
       <c r="P1" s="104"/>
       <c r="Q1" s="104"/>
     </row>
@@ -5648,11 +5653,14 @@
       </c>
       <c r="M2" s="104"/>
       <c r="N2" s="104"/>
+      <c r="O2" s="263">
+        <v>2818059.9699999997</v>
+      </c>
       <c r="P2" s="106"/>
       <c r="Q2" s="106"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="104"/>
       <c r="B3" s="104"/>
       <c r="C3" s="104"/>
@@ -5674,80 +5682,80 @@
       <c r="Q3" s="108"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="242" t="s">
+      <c r="A4" s="248" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="255" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="236" t="s">
+      <c r="C4" s="250" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="236" t="s">
+      <c r="D4" s="250" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="240" t="s">
+      <c r="E4" s="251" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="236" t="s">
+      <c r="F4" s="250" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="236" t="s">
+      <c r="G4" s="250" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="236" t="s">
+      <c r="H4" s="250" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="240" t="s">
+      <c r="I4" s="251" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="241" t="s">
+      <c r="J4" s="262" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="229" t="s">
+      <c r="K4" s="254" t="s">
         <v>72</v>
       </c>
-      <c r="L4" s="233" t="s">
+      <c r="L4" s="257" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="229" t="s">
+      <c r="M4" s="254" t="s">
         <v>74</v>
       </c>
-      <c r="N4" s="237" t="s">
+      <c r="N4" s="259" t="s">
         <v>75</v>
       </c>
       <c r="O4" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="P4" s="239" t="s">
+      <c r="P4" s="261" t="s">
         <v>77</v>
       </c>
-      <c r="Q4" s="233" t="s">
+      <c r="Q4" s="257" t="s">
         <v>78</v>
       </c>
       <c r="R4" s="4"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="234"/>
-      <c r="B5" s="232"/>
-      <c r="C5" s="234"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="230"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="234"/>
-      <c r="H5" s="234"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="230"/>
-      <c r="K5" s="230"/>
-      <c r="L5" s="234"/>
-      <c r="M5" s="230"/>
-      <c r="N5" s="238"/>
+      <c r="A5" s="249"/>
+      <c r="B5" s="256"/>
+      <c r="C5" s="249"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="252"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="252"/>
+      <c r="J5" s="252"/>
+      <c r="K5" s="252"/>
+      <c r="L5" s="249"/>
+      <c r="M5" s="252"/>
+      <c r="N5" s="260"/>
       <c r="O5" s="110" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="P5" s="232"/>
-      <c r="Q5" s="234"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="249"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
@@ -5785,27 +5793,27 @@
         <v>0</v>
       </c>
       <c r="L6" s="113">
-        <f t="shared" ref="L6:L34" si="2">O$3*F6%</f>
+        <f>O$3*F6%</f>
         <v>0</v>
       </c>
       <c r="M6" s="116">
-        <f>RESUMEN!H$92*F6%</f>
-        <v>0</v>
+        <f>O$2*F6%</f>
+        <v>30998.659670000001</v>
       </c>
       <c r="N6" s="117">
         <v>0</v>
       </c>
       <c r="O6" s="142">
-        <f t="shared" ref="O6:O34" si="3">ROUND(SUM(J6:N6),0) + R6</f>
-        <v>0.01</v>
+        <f>ROUND(SUM(J6:N6),0) + R6</f>
+        <v>30999.01</v>
       </c>
       <c r="P6" s="122">
-        <f t="shared" ref="P6:P36" si="4">ROUND(O6*6% + O6,0) + R6</f>
-        <v>0.01</v>
+        <f t="shared" ref="P6:P36" si="2">ROUND(O6*6% + O6,0) + R6</f>
+        <v>32859.01</v>
       </c>
       <c r="Q6" s="143">
-        <f t="shared" ref="Q6:Q36" si="5">ROUND(O6*3%,0) + O6</f>
-        <v>0.01</v>
+        <f t="shared" ref="Q6:Q36" si="3">ROUND(O6*3%,0) + O6</f>
+        <v>31929.01</v>
       </c>
       <c r="R6" s="74">
         <v>0.01</v>
@@ -5845,30 +5853,30 @@
         <v>0</v>
       </c>
       <c r="L7" s="166">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="L6:L34" si="4">O$3*F7%</f>
         <v>0</v>
       </c>
-      <c r="M7" s="167">
-        <f>RESUMEN!H$92*F7%</f>
-        <v>0</v>
+      <c r="M7" s="116">
+        <f t="shared" ref="M7:M34" si="5">O$2*F7%</f>
+        <v>25362.53973</v>
       </c>
       <c r="N7" s="168">
         <v>0</v>
       </c>
       <c r="O7" s="169">
+        <f t="shared" ref="O6:O34" si="6">ROUND(SUM(J7:N7),0) + R7</f>
+        <v>25363.02</v>
+      </c>
+      <c r="P7" s="170">
+        <f t="shared" si="2"/>
+        <v>26885.02</v>
+      </c>
+      <c r="Q7" s="171">
         <f t="shared" si="3"/>
-        <v>0.02</v>
-      </c>
-      <c r="P7" s="170">
-        <f t="shared" si="4"/>
-        <v>0.02</v>
-      </c>
-      <c r="Q7" s="171">
-        <f t="shared" si="5"/>
-        <v>0.02</v>
+        <v>26124.02</v>
       </c>
       <c r="R7" s="74">
-        <f t="shared" ref="R7:R35" si="6">R6+0.01</f>
+        <f t="shared" ref="R7:R35" si="7">R6+0.01</f>
         <v>0.02</v>
       </c>
       <c r="S7" s="74"/>
@@ -5909,30 +5917,30 @@
         <v>0</v>
       </c>
       <c r="L8" s="166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M8" s="167">
-        <f>RESUMEN!H$92*F8%</f>
-        <v>0</v>
+      <c r="M8" s="116">
+        <f t="shared" si="5"/>
+        <v>22544.479759999998</v>
       </c>
       <c r="N8" s="168">
         <v>0</v>
       </c>
       <c r="O8" s="169">
+        <f t="shared" si="6"/>
+        <v>22544.03</v>
+      </c>
+      <c r="P8" s="170">
+        <f t="shared" si="2"/>
+        <v>23897.03</v>
+      </c>
+      <c r="Q8" s="171">
         <f t="shared" si="3"/>
-        <v>0.03</v>
-      </c>
-      <c r="P8" s="170">
-        <f t="shared" si="4"/>
-        <v>0.03</v>
-      </c>
-      <c r="Q8" s="171">
-        <f t="shared" si="5"/>
-        <v>0.03</v>
+        <v>23220.03</v>
       </c>
       <c r="R8" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.03</v>
       </c>
     </row>
@@ -5970,30 +5978,30 @@
         <v>0</v>
       </c>
       <c r="L9" s="166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="167">
-        <f>RESUMEN!H$92*F9%</f>
-        <v>0</v>
+      <c r="M9" s="116">
+        <f t="shared" si="5"/>
+        <v>22544.479759999998</v>
       </c>
       <c r="N9" s="168">
         <v>0</v>
       </c>
       <c r="O9" s="169">
+        <f t="shared" si="6"/>
+        <v>22544.04</v>
+      </c>
+      <c r="P9" s="170">
+        <f t="shared" si="2"/>
+        <v>23897.040000000001</v>
+      </c>
+      <c r="Q9" s="171">
         <f t="shared" si="3"/>
-        <v>0.04</v>
-      </c>
-      <c r="P9" s="170">
-        <f t="shared" si="4"/>
-        <v>0.04</v>
-      </c>
-      <c r="Q9" s="171">
-        <f t="shared" si="5"/>
-        <v>0.04</v>
+        <v>23220.04</v>
       </c>
       <c r="R9" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
@@ -6030,30 +6038,30 @@
         <v>2019.8115</v>
       </c>
       <c r="L10" s="166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M10" s="167">
-        <f>RESUMEN!H$92*F10%</f>
-        <v>0</v>
+      <c r="M10" s="116">
+        <f t="shared" si="5"/>
+        <v>14090.299849999999</v>
       </c>
       <c r="N10" s="168">
         <v>0</v>
       </c>
       <c r="O10" s="169">
+        <f t="shared" si="6"/>
+        <v>83437.05</v>
+      </c>
+      <c r="P10" s="170">
+        <f t="shared" si="2"/>
+        <v>88443.05</v>
+      </c>
+      <c r="Q10" s="171">
         <f t="shared" si="3"/>
-        <v>69347.05</v>
-      </c>
-      <c r="P10" s="170">
-        <f t="shared" si="4"/>
-        <v>73508.05</v>
-      </c>
-      <c r="Q10" s="171">
-        <f t="shared" si="5"/>
-        <v>71427.05</v>
+        <v>85940.05</v>
       </c>
       <c r="R10" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
     </row>
@@ -6091,30 +6099,30 @@
         <v>0</v>
       </c>
       <c r="L11" s="166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M11" s="167">
-        <f>RESUMEN!H$92*F11%</f>
-        <v>0</v>
+      <c r="M11" s="116">
+        <f t="shared" si="5"/>
+        <v>14090.299849999999</v>
       </c>
       <c r="N11" s="168">
         <v>0</v>
       </c>
       <c r="O11" s="169">
+        <f t="shared" si="6"/>
+        <v>14090.06</v>
+      </c>
+      <c r="P11" s="170">
+        <f t="shared" si="2"/>
+        <v>14935.06</v>
+      </c>
+      <c r="Q11" s="171">
         <f t="shared" si="3"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="P11" s="170">
-        <f t="shared" si="4"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="Q11" s="171">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000005E-2</v>
+        <v>14513.06</v>
       </c>
       <c r="R11" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
@@ -6154,30 +6162,30 @@
         <v>0</v>
       </c>
       <c r="L12" s="166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="167">
-        <f>RESUMEN!H$92*F12%</f>
-        <v>0</v>
+      <c r="M12" s="116">
+        <f t="shared" si="5"/>
+        <v>14090.299849999999</v>
       </c>
       <c r="N12" s="168">
         <v>0</v>
       </c>
       <c r="O12" s="169">
+        <f t="shared" si="6"/>
+        <v>14090.07</v>
+      </c>
+      <c r="P12" s="170">
+        <f t="shared" si="2"/>
+        <v>14935.07</v>
+      </c>
+      <c r="Q12" s="171">
         <f t="shared" si="3"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="P12" s="170">
-        <f t="shared" si="4"/>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="Q12" s="171">
-        <f t="shared" si="5"/>
-        <v>7.0000000000000007E-2</v>
+        <v>14513.07</v>
       </c>
       <c r="R12" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -6185,59 +6193,59 @@
       <c r="A13" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="251" t="s">
+      <c r="B13" s="215" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="252">
+      <c r="C13" s="216">
         <v>1</v>
       </c>
-      <c r="D13" s="252" t="s">
+      <c r="D13" s="216" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="253" t="s">
+      <c r="E13" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="F13" s="254">
+      <c r="F13" s="218">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G13" s="255">
+      <c r="G13" s="219">
         <v>737279.08</v>
       </c>
-      <c r="H13" s="256"/>
-      <c r="I13" s="257"/>
-      <c r="J13" s="258">
+      <c r="H13" s="220"/>
+      <c r="I13" s="221"/>
+      <c r="J13" s="222">
         <f t="shared" si="0"/>
         <v>737279.08</v>
       </c>
-      <c r="K13" s="258">
+      <c r="K13" s="222">
         <f t="shared" si="1"/>
         <v>22118.372399999997</v>
       </c>
-      <c r="L13" s="255">
+      <c r="L13" s="219">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="222">
+        <f t="shared" si="5"/>
+        <v>123994.63868</v>
+      </c>
+      <c r="N13" s="223">
+        <v>0</v>
+      </c>
+      <c r="O13" s="224">
+        <f t="shared" si="6"/>
+        <v>883392.08</v>
+      </c>
+      <c r="P13" s="225">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="258">
-        <f>RESUMEN!H$92*F13%</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="259">
-        <v>0</v>
-      </c>
-      <c r="O13" s="260">
+        <v>936396.08</v>
+      </c>
+      <c r="Q13" s="226">
         <f t="shared" si="3"/>
-        <v>759397.08</v>
-      </c>
-      <c r="P13" s="261">
-        <f t="shared" si="4"/>
-        <v>804961.08</v>
-      </c>
-      <c r="Q13" s="262">
-        <f t="shared" si="5"/>
-        <v>782179.08</v>
+        <v>909894.08</v>
       </c>
       <c r="R13" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
@@ -6249,7 +6257,7 @@
         <v>102</v>
       </c>
       <c r="C14" s="135">
-        <f t="shared" ref="C14:C34" si="7">C13+1</f>
+        <f t="shared" ref="C14:C34" si="8">C13+1</f>
         <v>2</v>
       </c>
       <c r="D14" s="135" t="s">
@@ -6276,30 +6284,30 @@
         <v>3.9000000001396984E-3</v>
       </c>
       <c r="L14" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M14" s="116">
-        <f>RESUMEN!H$92*F14%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>126812.69864999998</v>
       </c>
       <c r="N14" s="117">
         <v>0</v>
       </c>
       <c r="O14" s="142">
+        <f t="shared" si="6"/>
+        <v>126813.09</v>
+      </c>
+      <c r="P14" s="122">
+        <f t="shared" si="2"/>
+        <v>134422.09</v>
+      </c>
+      <c r="Q14" s="143">
         <f t="shared" si="3"/>
-        <v>0.09</v>
-      </c>
-      <c r="P14" s="122">
-        <f t="shared" si="4"/>
-        <v>0.09</v>
-      </c>
-      <c r="Q14" s="143">
-        <f t="shared" si="5"/>
-        <v>0.09</v>
+        <v>130617.09</v>
       </c>
       <c r="R14" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
       <c r="U14" s="175" t="s">
@@ -6314,7 +6322,7 @@
         <v>105</v>
       </c>
       <c r="C15" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="D15" s="135" t="s">
@@ -6342,30 +6350,30 @@
         <v>114.12300000000018</v>
       </c>
       <c r="L15" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M15" s="116">
-        <f>RESUMEN!H$92*F15%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>126812.69864999998</v>
       </c>
       <c r="N15" s="117">
         <v>0</v>
       </c>
       <c r="O15" s="142">
+        <f t="shared" si="6"/>
+        <v>130731.1</v>
+      </c>
+      <c r="P15" s="122">
+        <f t="shared" si="2"/>
+        <v>138575.1</v>
+      </c>
+      <c r="Q15" s="143">
         <f t="shared" si="3"/>
-        <v>3918.1</v>
-      </c>
-      <c r="P15" s="122">
-        <f t="shared" si="4"/>
-        <v>4153.1000000000004</v>
-      </c>
-      <c r="Q15" s="143">
-        <f t="shared" si="5"/>
-        <v>4036.1</v>
+        <v>134653.1</v>
       </c>
       <c r="R15" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
@@ -6377,7 +6385,7 @@
         <v>108</v>
       </c>
       <c r="C16" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="D16" s="135" t="s">
@@ -6403,30 +6411,30 @@
         <v>5041.5032999999994</v>
       </c>
       <c r="L16" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M16" s="116">
-        <f>RESUMEN!H$92*F16%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>87359.859069999991</v>
       </c>
       <c r="N16" s="117">
         <v>0</v>
       </c>
       <c r="O16" s="142">
+        <f t="shared" si="6"/>
+        <v>260451.11</v>
+      </c>
+      <c r="P16" s="122">
+        <f t="shared" si="2"/>
+        <v>276078.11</v>
+      </c>
+      <c r="Q16" s="143">
         <f t="shared" si="3"/>
-        <v>173092.11</v>
-      </c>
-      <c r="P16" s="122">
-        <f t="shared" si="4"/>
-        <v>183478.11</v>
-      </c>
-      <c r="Q16" s="143">
-        <f t="shared" si="5"/>
-        <v>178285.11</v>
+        <v>268265.11</v>
       </c>
       <c r="R16" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
@@ -6434,62 +6442,62 @@
       <c r="A17" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="B17" s="251" t="s">
+      <c r="B17" s="215" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="252">
-        <f t="shared" si="7"/>
+      <c r="C17" s="216">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="D17" s="252" t="s">
+      <c r="D17" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="E17" s="253" t="s">
+      <c r="E17" s="217" t="s">
         <v>114</v>
       </c>
-      <c r="F17" s="254">
+      <c r="F17" s="218">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G17" s="255">
+      <c r="G17" s="219">
         <v>592471.12</v>
       </c>
-      <c r="H17" s="256">
+      <c r="H17" s="220">
         <v>240000</v>
       </c>
-      <c r="I17" s="257"/>
-      <c r="J17" s="258">
+      <c r="I17" s="221"/>
+      <c r="J17" s="222">
         <f t="shared" si="0"/>
         <v>352471.12</v>
       </c>
-      <c r="K17" s="258">
+      <c r="K17" s="222">
         <f t="shared" si="1"/>
         <v>10574.133599999999</v>
       </c>
-      <c r="L17" s="255">
+      <c r="L17" s="219">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="222">
+        <f t="shared" si="5"/>
+        <v>123994.63868</v>
+      </c>
+      <c r="N17" s="223">
+        <v>0</v>
+      </c>
+      <c r="O17" s="224">
+        <f t="shared" si="6"/>
+        <v>487040.12</v>
+      </c>
+      <c r="P17" s="225">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="258">
-        <f>RESUMEN!H$92*F17%</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="259">
-        <v>0</v>
-      </c>
-      <c r="O17" s="260">
+        <v>516263.12</v>
+      </c>
+      <c r="Q17" s="226">
         <f t="shared" si="3"/>
-        <v>363045.12</v>
-      </c>
-      <c r="P17" s="261">
-        <f t="shared" si="4"/>
-        <v>384828.12</v>
-      </c>
-      <c r="Q17" s="262">
-        <f t="shared" si="5"/>
-        <v>373936.12</v>
+        <v>501651.12</v>
       </c>
       <c r="R17" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
@@ -6497,60 +6505,60 @@
       <c r="A18" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="251" t="s">
+      <c r="B18" s="215" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="252">
-        <f t="shared" si="7"/>
+      <c r="C18" s="216">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="D18" s="252" t="s">
+      <c r="D18" s="216" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="253" t="s">
+      <c r="E18" s="217" t="s">
         <v>117</v>
       </c>
-      <c r="F18" s="254">
+      <c r="F18" s="218">
         <v>4.5</v>
       </c>
-      <c r="G18" s="255">
+      <c r="G18" s="219">
         <v>243943.13</v>
       </c>
-      <c r="H18" s="256"/>
-      <c r="I18" s="257"/>
-      <c r="J18" s="258">
+      <c r="H18" s="220"/>
+      <c r="I18" s="221"/>
+      <c r="J18" s="222">
         <f t="shared" si="0"/>
         <v>243943.13</v>
       </c>
-      <c r="K18" s="258">
+      <c r="K18" s="222">
         <f t="shared" si="1"/>
         <v>7318.2938999999997</v>
       </c>
-      <c r="L18" s="255">
+      <c r="L18" s="219">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="222">
+        <f t="shared" si="5"/>
+        <v>126812.69864999998</v>
+      </c>
+      <c r="N18" s="223">
+        <v>0</v>
+      </c>
+      <c r="O18" s="224">
+        <f t="shared" si="6"/>
+        <v>378074.13</v>
+      </c>
+      <c r="P18" s="225">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="258">
-        <f>RESUMEN!H$92*F18%</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="259">
-        <v>0</v>
-      </c>
-      <c r="O18" s="260">
+        <v>400759.13</v>
+      </c>
+      <c r="Q18" s="226">
         <f t="shared" si="3"/>
-        <v>251261.13</v>
-      </c>
-      <c r="P18" s="261">
-        <f t="shared" si="4"/>
-        <v>266337.13</v>
-      </c>
-      <c r="Q18" s="262">
-        <f t="shared" si="5"/>
-        <v>258799.13</v>
+        <v>389416.13</v>
       </c>
       <c r="R18" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
@@ -6562,7 +6570,7 @@
         <v>119</v>
       </c>
       <c r="C19" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="D19" s="135" t="s">
@@ -6589,30 +6597,30 @@
         <v>0</v>
       </c>
       <c r="L19" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M19" s="116">
-        <f>RESUMEN!H$92*F19%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>126812.69864999998</v>
       </c>
       <c r="N19" s="117">
         <v>0</v>
       </c>
       <c r="O19" s="142">
+        <f t="shared" si="6"/>
+        <v>126813.14</v>
+      </c>
+      <c r="P19" s="122">
+        <f t="shared" si="2"/>
+        <v>134422.14000000001</v>
+      </c>
+      <c r="Q19" s="143">
         <f t="shared" si="3"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="P19" s="122">
-        <f t="shared" si="4"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="Q19" s="143">
-        <f t="shared" si="5"/>
-        <v>0.13999999999999999</v>
+        <v>130617.14</v>
       </c>
       <c r="R19" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
@@ -6624,7 +6632,7 @@
         <v>121</v>
       </c>
       <c r="C20" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="D20" s="135" t="s">
@@ -6651,30 +6659,30 @@
         <v>0</v>
       </c>
       <c r="L20" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M20" s="116">
-        <f>RESUMEN!H$92*F20%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>87359.859069999991</v>
       </c>
       <c r="N20" s="117">
         <v>0</v>
       </c>
       <c r="O20" s="142">
+        <f t="shared" si="6"/>
+        <v>87360.15</v>
+      </c>
+      <c r="P20" s="122">
+        <f t="shared" si="2"/>
+        <v>92602.15</v>
+      </c>
+      <c r="Q20" s="143">
         <f t="shared" si="3"/>
-        <v>0.15</v>
-      </c>
-      <c r="P20" s="122">
-        <f t="shared" si="4"/>
-        <v>0.15</v>
-      </c>
-      <c r="Q20" s="143">
-        <f t="shared" si="5"/>
-        <v>0.15</v>
+        <v>89981.15</v>
       </c>
       <c r="R20" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
@@ -6686,7 +6694,7 @@
         <v>124</v>
       </c>
       <c r="C21" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="D21" s="135" t="s">
@@ -6715,30 +6723,30 @@
         <v>0</v>
       </c>
       <c r="L21" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M21" s="116">
-        <f>RESUMEN!H$92*F21%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>123994.63868</v>
       </c>
       <c r="N21" s="117">
         <v>0</v>
       </c>
       <c r="O21" s="142">
+        <f t="shared" si="6"/>
+        <v>123995.16</v>
+      </c>
+      <c r="P21" s="122">
+        <f t="shared" si="2"/>
+        <v>131435.16</v>
+      </c>
+      <c r="Q21" s="143">
         <f t="shared" si="3"/>
-        <v>0.16</v>
-      </c>
-      <c r="P21" s="122">
-        <f t="shared" si="4"/>
-        <v>0.16</v>
-      </c>
-      <c r="Q21" s="143">
-        <f t="shared" si="5"/>
-        <v>0.16</v>
+        <v>127715.16</v>
       </c>
       <c r="R21" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
       <c r="T21" s="121"/>
@@ -6751,7 +6759,7 @@
         <v>127</v>
       </c>
       <c r="C22" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="D22" s="135" t="s">
@@ -6779,30 +6787,30 @@
         <v>3619.3551000000002</v>
       </c>
       <c r="L22" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M22" s="116">
-        <f>RESUMEN!H$92*F22%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>126812.69864999998</v>
       </c>
       <c r="N22" s="117">
         <v>0</v>
       </c>
       <c r="O22" s="142">
+        <f t="shared" si="6"/>
+        <v>251077.17</v>
+      </c>
+      <c r="P22" s="122">
+        <f t="shared" si="2"/>
+        <v>266142.17</v>
+      </c>
+      <c r="Q22" s="143">
         <f t="shared" si="3"/>
-        <v>124265.17</v>
-      </c>
-      <c r="P22" s="122">
-        <f t="shared" si="4"/>
-        <v>131721.17000000001</v>
-      </c>
-      <c r="Q22" s="143">
-        <f t="shared" si="5"/>
-        <v>127993.17</v>
+        <v>258609.17</v>
       </c>
       <c r="R22" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
       <c r="T22" s="174"/>
@@ -6818,7 +6826,7 @@
         <v>131</v>
       </c>
       <c r="C23" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="D23" s="135" t="s">
@@ -6845,30 +6853,30 @@
         <v>0</v>
       </c>
       <c r="L23" s="166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M23" s="167">
-        <f>RESUMEN!H$92*F23%</f>
-        <v>0</v>
+      <c r="M23" s="116">
+        <f t="shared" si="5"/>
+        <v>126812.69864999998</v>
       </c>
       <c r="N23" s="168">
         <v>0</v>
       </c>
       <c r="O23" s="169">
+        <f t="shared" si="6"/>
+        <v>126813.18</v>
+      </c>
+      <c r="P23" s="170">
+        <f t="shared" si="2"/>
+        <v>134422.18</v>
+      </c>
+      <c r="Q23" s="171">
         <f t="shared" si="3"/>
-        <v>0.18000000000000002</v>
-      </c>
-      <c r="P23" s="170">
-        <f t="shared" si="4"/>
-        <v>0.18000000000000002</v>
-      </c>
-      <c r="Q23" s="171">
-        <f t="shared" si="5"/>
-        <v>0.18000000000000002</v>
+        <v>130617.18</v>
       </c>
       <c r="R23" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
       <c r="T23" s="174"/>
@@ -6881,7 +6889,7 @@
         <v>133</v>
       </c>
       <c r="C24" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="D24" s="135" t="s">
@@ -6910,30 +6918,30 @@
         <v>6.6000000000349243E-3</v>
       </c>
       <c r="L24" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M24" s="116">
-        <f>RESUMEN!H$92*F24%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>87359.859069999991</v>
       </c>
       <c r="N24" s="117">
         <v>0</v>
       </c>
       <c r="O24" s="142">
+        <f t="shared" si="6"/>
+        <v>87360.19</v>
+      </c>
+      <c r="P24" s="122">
+        <f t="shared" si="2"/>
+        <v>92602.19</v>
+      </c>
+      <c r="Q24" s="143">
         <f t="shared" si="3"/>
-        <v>0.19000000000000003</v>
-      </c>
-      <c r="P24" s="122">
-        <f t="shared" si="4"/>
-        <v>0.19000000000000003</v>
-      </c>
-      <c r="Q24" s="143">
-        <f t="shared" si="5"/>
-        <v>0.19000000000000003</v>
+        <v>89981.19</v>
       </c>
       <c r="R24" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.19000000000000003</v>
       </c>
       <c r="T24" s="174"/>
@@ -6946,7 +6954,7 @@
         <v>135</v>
       </c>
       <c r="C25" s="200">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="D25" s="200" t="s">
@@ -6970,30 +6978,30 @@
         <v>8512.2659999999996</v>
       </c>
       <c r="L25" s="166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M25" s="167">
-        <f>RESUMEN!H$92*F25%</f>
-        <v>0</v>
+      <c r="M25" s="116">
+        <f t="shared" si="5"/>
+        <v>123994.63868</v>
       </c>
       <c r="N25" s="168">
         <v>0</v>
       </c>
       <c r="O25" s="169">
+        <f t="shared" si="6"/>
+        <v>416249.2</v>
+      </c>
+      <c r="P25" s="170">
+        <f t="shared" si="2"/>
+        <v>441224.2</v>
+      </c>
+      <c r="Q25" s="171">
         <f t="shared" si="3"/>
-        <v>292254.2</v>
-      </c>
-      <c r="P25" s="170">
-        <f t="shared" si="4"/>
-        <v>309789.2</v>
-      </c>
-      <c r="Q25" s="171">
-        <f t="shared" si="5"/>
-        <v>301022.2</v>
+        <v>428736.2</v>
       </c>
       <c r="R25" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="T25" s="175" t="s">
@@ -7010,7 +7018,7 @@
         <v>139</v>
       </c>
       <c r="C26" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="D26" s="135" t="s">
@@ -7039,30 +7047,30 @@
         <v>6.6000000000349243E-3</v>
       </c>
       <c r="L26" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M26" s="116">
-        <f>RESUMEN!H$92*F26%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>126812.69864999998</v>
       </c>
       <c r="N26" s="117">
         <v>0</v>
       </c>
       <c r="O26" s="142">
+        <f t="shared" si="6"/>
+        <v>126813.21</v>
+      </c>
+      <c r="P26" s="122">
+        <f t="shared" si="2"/>
+        <v>134422.21</v>
+      </c>
+      <c r="Q26" s="143">
         <f t="shared" si="3"/>
-        <v>0.21000000000000005</v>
-      </c>
-      <c r="P26" s="122">
-        <f t="shared" si="4"/>
-        <v>0.21000000000000005</v>
-      </c>
-      <c r="Q26" s="143">
-        <f t="shared" si="5"/>
-        <v>0.21000000000000005</v>
+        <v>130617.21</v>
       </c>
       <c r="R26" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.21000000000000005</v>
       </c>
       <c r="T26" s="174"/>
@@ -7075,7 +7083,7 @@
         <v>142</v>
       </c>
       <c r="C27" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="D27" s="135" t="s">
@@ -7104,30 +7112,30 @@
         <v>4227.0686999999998</v>
       </c>
       <c r="L27" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M27" s="116">
-        <f>RESUMEN!H$92*F27%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>126812.69864999998</v>
       </c>
       <c r="N27" s="117">
         <v>0</v>
       </c>
       <c r="O27" s="142">
+        <f t="shared" si="6"/>
+        <v>271942.21999999997</v>
+      </c>
+      <c r="P27" s="122">
+        <f t="shared" si="2"/>
+        <v>288259.21999999997</v>
+      </c>
+      <c r="Q27" s="143">
         <f t="shared" si="3"/>
-        <v>145129.22</v>
-      </c>
-      <c r="P27" s="122">
-        <f t="shared" si="4"/>
-        <v>153837.22</v>
-      </c>
-      <c r="Q27" s="143">
-        <f t="shared" si="5"/>
-        <v>149483.22</v>
+        <v>280100.21999999997</v>
       </c>
       <c r="R27" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.22000000000000006</v>
       </c>
       <c r="T27" s="208"/>
@@ -7140,7 +7148,7 @@
         <v>146</v>
       </c>
       <c r="C28" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="D28" s="135" t="s">
@@ -7169,30 +7177,30 @@
         <v>0</v>
       </c>
       <c r="L28" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M28" s="116">
-        <f>RESUMEN!H$92*F28%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>87359.859069999991</v>
       </c>
       <c r="N28" s="117">
         <v>0</v>
       </c>
       <c r="O28" s="142">
+        <f t="shared" si="6"/>
+        <v>84739.23</v>
+      </c>
+      <c r="P28" s="122">
+        <f t="shared" si="2"/>
+        <v>89824.23</v>
+      </c>
+      <c r="Q28" s="143">
         <f t="shared" si="3"/>
-        <v>-2620.77</v>
-      </c>
-      <c r="P28" s="122">
-        <f t="shared" si="4"/>
-        <v>-2777.77</v>
-      </c>
-      <c r="Q28" s="143">
-        <f t="shared" si="5"/>
-        <v>-2699.77</v>
+        <v>87281.23</v>
       </c>
       <c r="R28" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
@@ -7204,7 +7212,7 @@
         <v>150</v>
       </c>
       <c r="C29" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="D29" s="135" t="s">
@@ -7231,30 +7239,30 @@
         <v>9.6000000002095468E-3</v>
       </c>
       <c r="L29" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M29" s="116">
-        <f>RESUMEN!H$92*F29%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>191628.07796</v>
       </c>
       <c r="N29" s="117">
         <v>0</v>
       </c>
       <c r="O29" s="142">
+        <f t="shared" si="6"/>
+        <v>191628.24</v>
+      </c>
+      <c r="P29" s="122">
+        <f t="shared" si="2"/>
+        <v>203126.24</v>
+      </c>
+      <c r="Q29" s="143">
         <f t="shared" si="3"/>
-        <v>0.24000000000000007</v>
-      </c>
-      <c r="P29" s="122">
-        <f t="shared" si="4"/>
-        <v>0.24000000000000007</v>
-      </c>
-      <c r="Q29" s="143">
-        <f t="shared" si="5"/>
-        <v>0.24000000000000007</v>
+        <v>197377.24</v>
       </c>
       <c r="R29" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
@@ -7266,7 +7274,7 @@
         <v>151</v>
       </c>
       <c r="C30" s="200">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="D30" s="200" t="s">
@@ -7292,30 +7300,30 @@
         <v>7272.7874999999995</v>
       </c>
       <c r="L30" s="166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M30" s="167">
-        <f>RESUMEN!H$92*F30%</f>
-        <v>0</v>
+      <c r="M30" s="116">
+        <f t="shared" si="5"/>
+        <v>194446.13793</v>
       </c>
       <c r="N30" s="168">
         <v>0</v>
       </c>
       <c r="O30" s="169">
+        <f t="shared" si="6"/>
+        <v>444145.25</v>
+      </c>
+      <c r="P30" s="170">
+        <f t="shared" si="2"/>
+        <v>470794.25</v>
+      </c>
+      <c r="Q30" s="171">
         <f t="shared" si="3"/>
-        <v>249699.25</v>
-      </c>
-      <c r="P30" s="170">
-        <f t="shared" si="4"/>
-        <v>264681.25</v>
-      </c>
-      <c r="Q30" s="171">
-        <f t="shared" si="5"/>
-        <v>257190.25</v>
+        <v>457469.25</v>
       </c>
       <c r="R30" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
@@ -7327,7 +7335,7 @@
         <v>153</v>
       </c>
       <c r="C31" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="D31" s="135" t="s">
@@ -7356,30 +7364,30 @@
         <v>0</v>
       </c>
       <c r="L31" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M31" s="116">
-        <f>RESUMEN!H$92*F31%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>126812.69864999998</v>
       </c>
       <c r="N31" s="117">
         <v>0</v>
       </c>
       <c r="O31" s="142">
+        <f t="shared" si="6"/>
+        <v>126813.26</v>
+      </c>
+      <c r="P31" s="122">
+        <f t="shared" si="2"/>
+        <v>134422.26</v>
+      </c>
+      <c r="Q31" s="143">
         <f t="shared" si="3"/>
-        <v>0.26000000000000006</v>
-      </c>
-      <c r="P31" s="122">
-        <f t="shared" si="4"/>
-        <v>0.26000000000000006</v>
-      </c>
-      <c r="Q31" s="143">
-        <f t="shared" si="5"/>
-        <v>0.26000000000000006</v>
+        <v>130617.26</v>
       </c>
       <c r="R31" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
@@ -7391,7 +7399,7 @@
         <v>156</v>
       </c>
       <c r="C32" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="D32" s="135" t="s">
@@ -7419,30 +7427,30 @@
         <v>2415.3680999999997</v>
       </c>
       <c r="L32" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M32" s="116">
-        <f>RESUMEN!H$92*F32%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>87359.859069999991</v>
       </c>
       <c r="N32" s="117">
         <v>0</v>
       </c>
       <c r="O32" s="142">
+        <f t="shared" si="6"/>
+        <v>170287.27</v>
+      </c>
+      <c r="P32" s="122">
+        <f t="shared" si="2"/>
+        <v>180505.27</v>
+      </c>
+      <c r="Q32" s="143">
         <f t="shared" si="3"/>
-        <v>82928.27</v>
-      </c>
-      <c r="P32" s="122">
-        <f t="shared" si="4"/>
-        <v>87904.27</v>
-      </c>
-      <c r="Q32" s="143">
-        <f t="shared" si="5"/>
-        <v>85416.27</v>
+        <v>175396.27</v>
       </c>
       <c r="R32" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
@@ -7450,60 +7458,60 @@
       <c r="A33" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="251" t="s">
+      <c r="B33" s="215" t="s">
         <v>159</v>
       </c>
-      <c r="C33" s="252">
-        <f t="shared" si="7"/>
+      <c r="C33" s="216">
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="D33" s="252" t="s">
+      <c r="D33" s="216" t="s">
         <v>160</v>
       </c>
-      <c r="E33" s="263" t="s">
+      <c r="E33" s="227" t="s">
         <v>161</v>
       </c>
-      <c r="F33" s="254">
+      <c r="F33" s="218">
         <v>4.5</v>
       </c>
-      <c r="G33" s="255">
+      <c r="G33" s="219">
         <v>573819.28</v>
       </c>
-      <c r="H33" s="256"/>
-      <c r="I33" s="257"/>
-      <c r="J33" s="258">
+      <c r="H33" s="220"/>
+      <c r="I33" s="221"/>
+      <c r="J33" s="222">
         <f t="shared" si="0"/>
         <v>573819.28</v>
       </c>
-      <c r="K33" s="258">
+      <c r="K33" s="222">
         <f t="shared" si="1"/>
         <v>17214.578399999999</v>
       </c>
-      <c r="L33" s="255">
+      <c r="L33" s="219">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="222">
+        <f t="shared" si="5"/>
+        <v>126812.69864999998</v>
+      </c>
+      <c r="N33" s="225">
+        <v>42488</v>
+      </c>
+      <c r="O33" s="224">
+        <f t="shared" si="6"/>
+        <v>760335.28</v>
+      </c>
+      <c r="P33" s="225">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M33" s="258">
-        <f>RESUMEN!H$92*F33%</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="261">
-        <v>42488</v>
-      </c>
-      <c r="O33" s="260">
+        <v>805955.28</v>
+      </c>
+      <c r="Q33" s="226">
         <f t="shared" si="3"/>
-        <v>633522.28</v>
-      </c>
-      <c r="P33" s="261">
-        <f t="shared" si="4"/>
-        <v>671534.28</v>
-      </c>
-      <c r="Q33" s="262">
-        <f t="shared" si="5"/>
-        <v>652528.28</v>
+        <v>783145.28</v>
       </c>
       <c r="R33" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
@@ -7515,7 +7523,7 @@
         <v>162</v>
       </c>
       <c r="C34" s="135">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="D34" s="135" t="s">
@@ -7542,30 +7550,30 @@
         <v>0</v>
       </c>
       <c r="L34" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M34" s="116">
-        <f>RESUMEN!H$92*F34%</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>87359.859069999991</v>
       </c>
       <c r="N34" s="117">
         <v>0</v>
       </c>
       <c r="O34" s="142">
+        <f t="shared" si="6"/>
+        <v>87360.29</v>
+      </c>
+      <c r="P34" s="122">
+        <f t="shared" si="2"/>
+        <v>92602.29</v>
+      </c>
+      <c r="Q34" s="143">
         <f t="shared" si="3"/>
-        <v>0.29000000000000009</v>
-      </c>
-      <c r="P34" s="122">
-        <f t="shared" si="4"/>
-        <v>0.29000000000000009</v>
-      </c>
-      <c r="Q34" s="143">
-        <f t="shared" si="5"/>
-        <v>0.29000000000000009</v>
+        <v>89981.29</v>
       </c>
       <c r="R34" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
@@ -7596,15 +7604,15 @@
       </c>
       <c r="O35" s="118"/>
       <c r="P35" s="117">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.3000000000000001</v>
       </c>
       <c r="Q35" s="119">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R35" s="74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
@@ -7644,11 +7652,11 @@
         <v>0</v>
       </c>
       <c r="P36" s="117">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q36" s="119">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R36" s="74"/>
@@ -7659,52 +7667,52 @@
       <c r="D37" s="129"/>
       <c r="E37" s="129"/>
       <c r="F37" s="137">
-        <f t="shared" ref="F37:Q37" si="8">SUM(F6:F36)</f>
+        <f t="shared" ref="F37:Q37" si="9">SUM(F6:F36)</f>
         <v>99.999999999999986</v>
       </c>
       <c r="G37" s="130">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5675667.3500000006</v>
       </c>
       <c r="H37" s="131">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2663365.1799999997</v>
       </c>
       <c r="I37" s="130">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J37" s="131">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3012302.169999999</v>
       </c>
       <c r="K37" s="130">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>90447.688199999975</v>
       </c>
       <c r="L37" s="131">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M37" s="130">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>2818059.9699999997</v>
       </c>
       <c r="N37" s="131">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>42488</v>
       </c>
       <c r="O37" s="132">
-        <f t="shared" si="8"/>
-        <v>3145240.3499999996</v>
+        <f t="shared" si="9"/>
+        <v>5963301.3499999996</v>
       </c>
       <c r="P37" s="132">
-        <f t="shared" si="8"/>
-        <v>3333957.6499999994</v>
+        <f t="shared" si="9"/>
+        <v>6321106.6500000004</v>
       </c>
       <c r="Q37" s="132">
-        <f t="shared" si="8"/>
-        <v>3239598.3499999996</v>
+        <f t="shared" si="9"/>
+        <v>6142198.3500000006</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7721,95 +7729,95 @@
       <c r="Q39" s="4"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="228" t="s">
+      <c r="D40" s="253" t="s">
         <v>164</v>
       </c>
-      <c r="E40" s="209"/>
-      <c r="F40" s="209"/>
-      <c r="G40" s="209"/>
-      <c r="H40" s="209"/>
-      <c r="I40" s="209"/>
-      <c r="J40" s="209"/>
-      <c r="K40" s="209"/>
-      <c r="L40" s="209"/>
-      <c r="M40" s="209"/>
-      <c r="N40" s="209"/>
-      <c r="O40" s="209"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="230"/>
+      <c r="H40" s="230"/>
+      <c r="I40" s="230"/>
+      <c r="J40" s="230"/>
+      <c r="K40" s="230"/>
+      <c r="L40" s="230"/>
+      <c r="M40" s="230"/>
+      <c r="N40" s="230"/>
+      <c r="O40" s="230"/>
       <c r="Q40" s="4"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="209"/>
-      <c r="E41" s="209"/>
-      <c r="F41" s="209"/>
-      <c r="G41" s="209"/>
-      <c r="H41" s="209"/>
-      <c r="I41" s="209"/>
-      <c r="J41" s="209"/>
-      <c r="K41" s="209"/>
-      <c r="L41" s="209"/>
-      <c r="M41" s="209"/>
-      <c r="N41" s="209"/>
-      <c r="O41" s="209"/>
+      <c r="D41" s="230"/>
+      <c r="E41" s="230"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="230"/>
+      <c r="K41" s="230"/>
+      <c r="L41" s="230"/>
+      <c r="M41" s="230"/>
+      <c r="N41" s="230"/>
+      <c r="O41" s="230"/>
       <c r="Q41" s="4"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="209"/>
-      <c r="E42" s="209"/>
-      <c r="F42" s="209"/>
-      <c r="G42" s="209"/>
-      <c r="H42" s="209"/>
-      <c r="I42" s="209"/>
-      <c r="J42" s="209"/>
-      <c r="K42" s="209"/>
-      <c r="L42" s="209"/>
-      <c r="M42" s="209"/>
-      <c r="N42" s="209"/>
-      <c r="O42" s="209"/>
+      <c r="D42" s="230"/>
+      <c r="E42" s="230"/>
+      <c r="F42" s="230"/>
+      <c r="G42" s="230"/>
+      <c r="H42" s="230"/>
+      <c r="I42" s="230"/>
+      <c r="J42" s="230"/>
+      <c r="K42" s="230"/>
+      <c r="L42" s="230"/>
+      <c r="M42" s="230"/>
+      <c r="N42" s="230"/>
+      <c r="O42" s="230"/>
       <c r="Q42" s="4"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="209"/>
-      <c r="E43" s="209"/>
-      <c r="F43" s="209"/>
-      <c r="G43" s="209"/>
-      <c r="H43" s="209"/>
-      <c r="I43" s="209"/>
-      <c r="J43" s="209"/>
-      <c r="K43" s="209"/>
-      <c r="L43" s="209"/>
-      <c r="M43" s="209"/>
-      <c r="N43" s="209"/>
-      <c r="O43" s="209"/>
+      <c r="D43" s="230"/>
+      <c r="E43" s="230"/>
+      <c r="F43" s="230"/>
+      <c r="G43" s="230"/>
+      <c r="H43" s="230"/>
+      <c r="I43" s="230"/>
+      <c r="J43" s="230"/>
+      <c r="K43" s="230"/>
+      <c r="L43" s="230"/>
+      <c r="M43" s="230"/>
+      <c r="N43" s="230"/>
+      <c r="O43" s="230"/>
       <c r="Q43" s="4"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="209"/>
-      <c r="E44" s="209"/>
-      <c r="F44" s="209"/>
-      <c r="G44" s="209"/>
-      <c r="H44" s="209"/>
-      <c r="I44" s="209"/>
-      <c r="J44" s="209"/>
-      <c r="K44" s="209"/>
-      <c r="L44" s="209"/>
-      <c r="M44" s="209"/>
-      <c r="N44" s="209"/>
-      <c r="O44" s="209"/>
+      <c r="D44" s="230"/>
+      <c r="E44" s="230"/>
+      <c r="F44" s="230"/>
+      <c r="G44" s="230"/>
+      <c r="H44" s="230"/>
+      <c r="I44" s="230"/>
+      <c r="J44" s="230"/>
+      <c r="K44" s="230"/>
+      <c r="L44" s="230"/>
+      <c r="M44" s="230"/>
+      <c r="N44" s="230"/>
+      <c r="O44" s="230"/>
       <c r="Q44" s="4"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="209"/>
-      <c r="E45" s="209"/>
-      <c r="F45" s="209"/>
-      <c r="G45" s="209"/>
-      <c r="H45" s="209"/>
-      <c r="I45" s="209"/>
-      <c r="J45" s="209"/>
-      <c r="K45" s="209"/>
-      <c r="L45" s="209"/>
-      <c r="M45" s="209"/>
-      <c r="N45" s="209"/>
-      <c r="O45" s="209"/>
+      <c r="D45" s="230"/>
+      <c r="E45" s="230"/>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="230"/>
+      <c r="K45" s="230"/>
+      <c r="L45" s="230"/>
+      <c r="M45" s="230"/>
+      <c r="N45" s="230"/>
+      <c r="O45" s="230"/>
       <c r="Q45" s="4"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13280,11 +13288,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
     <mergeCell ref="D40:O45"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
@@ -13298,6 +13301,11 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/ILLIA/Junio/ILLIA-JUNIO.xlsx
+++ b/ILLIA/Junio/ILLIA-JUNIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DD2DB0-620C-470F-A29C-E378D842E1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AB5DEC-80D1-4842-844A-F8E2B2AF7A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1789,15 +1789,26 @@
     <xf numFmtId="167" fontId="21" fillId="18" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="170" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
@@ -1810,43 +1821,23 @@
     <xf numFmtId="165" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1854,8 +1845,12 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1864,10 +1859,15 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2123,11 +2123,11 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
-      <c r="B3" s="229" t="s">
+      <c r="B3" s="237" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="230"/>
-      <c r="D3" s="230"/>
+      <c r="C3" s="231"/>
+      <c r="D3" s="231"/>
       <c r="E3" s="9"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -2135,9 +2135,9 @@
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
-      <c r="B4" s="231"/>
-      <c r="C4" s="231"/>
-      <c r="D4" s="231"/>
+      <c r="B4" s="238"/>
+      <c r="C4" s="238"/>
+      <c r="D4" s="238"/>
       <c r="E4" s="9"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -2175,13 +2175,13 @@
       <c r="I6" s="156"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="244" t="s">
+      <c r="A7" s="247" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="231"/>
-      <c r="C7" s="231"/>
-      <c r="D7" s="231"/>
-      <c r="E7" s="245"/>
+      <c r="B7" s="238"/>
+      <c r="C7" s="238"/>
+      <c r="D7" s="238"/>
+      <c r="E7" s="248"/>
       <c r="F7" s="17"/>
       <c r="G7" s="157"/>
       <c r="H7" s="157"/>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="237" t="s">
+      <c r="B9" s="242" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="230"/>
+      <c r="C9" s="231"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -2206,8 +2206,8 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="230"/>
-      <c r="C10" s="230"/>
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -2216,8 +2216,8 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="230"/>
-      <c r="C11" s="230"/>
+      <c r="B11" s="231"/>
+      <c r="C11" s="231"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -2236,43 +2236,43 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="246" t="s">
+      <c r="A14" s="230" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="230"/>
-      <c r="C14" s="230"/>
-      <c r="D14" s="230"/>
-      <c r="E14" s="230"/>
+      <c r="B14" s="231"/>
+      <c r="C14" s="231"/>
+      <c r="D14" s="231"/>
+      <c r="E14" s="231"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="230"/>
-      <c r="B15" s="230"/>
-      <c r="C15" s="230"/>
-      <c r="D15" s="230"/>
-      <c r="E15" s="230"/>
+      <c r="A15" s="231"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="231"/>
+      <c r="D15" s="231"/>
+      <c r="E15" s="231"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="230"/>
-      <c r="B16" s="230"/>
-      <c r="C16" s="230"/>
-      <c r="D16" s="230"/>
-      <c r="E16" s="230"/>
+      <c r="A16" s="231"/>
+      <c r="B16" s="231"/>
+      <c r="C16" s="231"/>
+      <c r="D16" s="231"/>
+      <c r="E16" s="231"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="230"/>
-      <c r="B17" s="230"/>
-      <c r="C17" s="230"/>
-      <c r="D17" s="230"/>
-      <c r="E17" s="230"/>
+      <c r="A17" s="231"/>
+      <c r="B17" s="231"/>
+      <c r="C17" s="231"/>
+      <c r="D17" s="231"/>
+      <c r="E17" s="231"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
@@ -2796,7 +2796,7 @@
       <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="242" t="s">
+      <c r="A44" s="246" t="s">
         <v>23</v>
       </c>
       <c r="B44" s="233"/>
@@ -3010,7 +3010,7 @@
       <c r="Z54" s="4"/>
     </row>
     <row r="55" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="241" t="s">
+      <c r="A55" s="245" t="s">
         <v>168</v>
       </c>
       <c r="B55" s="233"/>
@@ -3230,7 +3230,7 @@
       <c r="H63" s="4"/>
     </row>
     <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="241"/>
+      <c r="A64" s="245"/>
       <c r="B64" s="233"/>
       <c r="C64" s="25"/>
       <c r="D64" s="188"/>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="66" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="232"/>
-      <c r="B66" s="234"/>
+      <c r="B66" s="239"/>
       <c r="C66" s="53"/>
-      <c r="D66" s="239"/>
-      <c r="E66" s="247"/>
+      <c r="D66" s="244"/>
+      <c r="E66" s="235"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
@@ -3314,11 +3314,11 @@
       <c r="Z66" s="4"/>
     </row>
     <row r="67" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="235"/>
-      <c r="B67" s="236"/>
+      <c r="A67" s="240"/>
+      <c r="B67" s="241"/>
       <c r="C67" s="53"/>
-      <c r="D67" s="240"/>
-      <c r="E67" s="240"/>
+      <c r="D67" s="236"/>
+      <c r="E67" s="236"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
@@ -3545,7 +3545,7 @@
       <c r="Z75" s="4"/>
     </row>
     <row r="76" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="243"/>
+      <c r="A76" s="234"/>
       <c r="B76" s="233"/>
       <c r="C76" s="58"/>
       <c r="D76" s="194"/>
@@ -3629,7 +3629,7 @@
       <c r="E80" s="62"/>
     </row>
     <row r="81" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="243"/>
+      <c r="A81" s="234"/>
       <c r="B81" s="233"/>
       <c r="C81" s="25"/>
       <c r="D81" s="190"/>
@@ -4591,16 +4591,16 @@
     <row r="132" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="133" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="238" t="s">
+      <c r="A134" s="243" t="s">
         <v>59</v>
       </c>
-      <c r="B134" s="230"/>
-      <c r="C134" s="230"/>
+      <c r="B134" s="231"/>
+      <c r="C134" s="231"/>
     </row>
     <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="230"/>
-      <c r="B135" s="230"/>
-      <c r="C135" s="230"/>
+      <c r="A135" s="231"/>
+      <c r="B135" s="231"/>
+      <c r="C135" s="231"/>
     </row>
     <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="25"/>
@@ -5557,14 +5557,6 @@
     <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="A72:B72"/>
     <mergeCell ref="B3:D4"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A66:B67"/>
@@ -5581,6 +5573,14 @@
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="A72:B72"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5620,16 +5620,16 @@
       <c r="C1" s="104"/>
       <c r="D1" s="104"/>
       <c r="E1" s="104"/>
-      <c r="F1" s="258"/>
-      <c r="G1" s="230"/>
-      <c r="H1" s="230"/>
-      <c r="I1" s="230"/>
-      <c r="J1" s="230"/>
-      <c r="K1" s="230"/>
-      <c r="L1" s="230"/>
-      <c r="M1" s="230"/>
-      <c r="N1" s="230"/>
-      <c r="O1" s="230"/>
+      <c r="F1" s="256"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
+      <c r="K1" s="231"/>
+      <c r="L1" s="231"/>
+      <c r="M1" s="231"/>
+      <c r="N1" s="231"/>
+      <c r="O1" s="231"/>
       <c r="P1" s="104"/>
       <c r="Q1" s="104"/>
     </row>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="M2" s="104"/>
       <c r="N2" s="104"/>
-      <c r="O2" s="263">
+      <c r="O2" s="229">
         <v>2818059.9699999997</v>
       </c>
       <c r="P2" s="106"/>
@@ -5682,80 +5682,80 @@
       <c r="Q3" s="108"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="248" t="s">
+      <c r="A4" s="263" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="255" t="s">
+      <c r="B4" s="252" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="250" t="s">
+      <c r="C4" s="257" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="250" t="s">
+      <c r="D4" s="257" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="251" t="s">
+      <c r="E4" s="261" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="250" t="s">
+      <c r="F4" s="257" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="250" t="s">
+      <c r="G4" s="257" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="250" t="s">
+      <c r="H4" s="257" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="251" t="s">
+      <c r="I4" s="261" t="s">
         <v>70</v>
       </c>
       <c r="J4" s="262" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="254" t="s">
+      <c r="K4" s="250" t="s">
         <v>72</v>
       </c>
-      <c r="L4" s="257" t="s">
+      <c r="L4" s="254" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="254" t="s">
+      <c r="M4" s="250" t="s">
         <v>74</v>
       </c>
-      <c r="N4" s="259" t="s">
+      <c r="N4" s="258" t="s">
         <v>75</v>
       </c>
       <c r="O4" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="P4" s="261" t="s">
+      <c r="P4" s="260" t="s">
         <v>77</v>
       </c>
-      <c r="Q4" s="257" t="s">
+      <c r="Q4" s="254" t="s">
         <v>78</v>
       </c>
       <c r="R4" s="4"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="249"/>
-      <c r="B5" s="256"/>
-      <c r="C5" s="249"/>
-      <c r="D5" s="249"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="249"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="252"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="249"/>
-      <c r="M5" s="252"/>
-      <c r="N5" s="260"/>
+      <c r="A5" s="255"/>
+      <c r="B5" s="253"/>
+      <c r="C5" s="255"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="255"/>
+      <c r="M5" s="251"/>
+      <c r="N5" s="259"/>
       <c r="O5" s="110" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="P5" s="256"/>
-      <c r="Q5" s="249"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="255"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
@@ -5853,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="166">
-        <f t="shared" ref="L6:L34" si="4">O$3*F7%</f>
+        <f t="shared" ref="L7:L34" si="4">O$3*F7%</f>
         <v>0</v>
       </c>
       <c r="M7" s="116">
@@ -5864,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="169">
-        <f t="shared" ref="O6:O34" si="6">ROUND(SUM(J7:N7),0) + R7</f>
+        <f t="shared" ref="O7:O34" si="6">ROUND(SUM(J7:N7),0) + R7</f>
         <v>25363.02</v>
       </c>
       <c r="P7" s="170">
@@ -7729,95 +7729,95 @@
       <c r="Q39" s="4"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="253" t="s">
+      <c r="D40" s="249" t="s">
         <v>164</v>
       </c>
-      <c r="E40" s="230"/>
-      <c r="F40" s="230"/>
-      <c r="G40" s="230"/>
-      <c r="H40" s="230"/>
-      <c r="I40" s="230"/>
-      <c r="J40" s="230"/>
-      <c r="K40" s="230"/>
-      <c r="L40" s="230"/>
-      <c r="M40" s="230"/>
-      <c r="N40" s="230"/>
-      <c r="O40" s="230"/>
+      <c r="E40" s="231"/>
+      <c r="F40" s="231"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="231"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="231"/>
+      <c r="M40" s="231"/>
+      <c r="N40" s="231"/>
+      <c r="O40" s="231"/>
       <c r="Q40" s="4"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="230"/>
-      <c r="E41" s="230"/>
-      <c r="F41" s="230"/>
-      <c r="G41" s="230"/>
-      <c r="H41" s="230"/>
-      <c r="I41" s="230"/>
-      <c r="J41" s="230"/>
-      <c r="K41" s="230"/>
-      <c r="L41" s="230"/>
-      <c r="M41" s="230"/>
-      <c r="N41" s="230"/>
-      <c r="O41" s="230"/>
+      <c r="D41" s="231"/>
+      <c r="E41" s="231"/>
+      <c r="F41" s="231"/>
+      <c r="G41" s="231"/>
+      <c r="H41" s="231"/>
+      <c r="I41" s="231"/>
+      <c r="J41" s="231"/>
+      <c r="K41" s="231"/>
+      <c r="L41" s="231"/>
+      <c r="M41" s="231"/>
+      <c r="N41" s="231"/>
+      <c r="O41" s="231"/>
       <c r="Q41" s="4"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="230"/>
-      <c r="E42" s="230"/>
-      <c r="F42" s="230"/>
-      <c r="G42" s="230"/>
-      <c r="H42" s="230"/>
-      <c r="I42" s="230"/>
-      <c r="J42" s="230"/>
-      <c r="K42" s="230"/>
-      <c r="L42" s="230"/>
-      <c r="M42" s="230"/>
-      <c r="N42" s="230"/>
-      <c r="O42" s="230"/>
+      <c r="D42" s="231"/>
+      <c r="E42" s="231"/>
+      <c r="F42" s="231"/>
+      <c r="G42" s="231"/>
+      <c r="H42" s="231"/>
+      <c r="I42" s="231"/>
+      <c r="J42" s="231"/>
+      <c r="K42" s="231"/>
+      <c r="L42" s="231"/>
+      <c r="M42" s="231"/>
+      <c r="N42" s="231"/>
+      <c r="O42" s="231"/>
       <c r="Q42" s="4"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="230"/>
-      <c r="E43" s="230"/>
-      <c r="F43" s="230"/>
-      <c r="G43" s="230"/>
-      <c r="H43" s="230"/>
-      <c r="I43" s="230"/>
-      <c r="J43" s="230"/>
-      <c r="K43" s="230"/>
-      <c r="L43" s="230"/>
-      <c r="M43" s="230"/>
-      <c r="N43" s="230"/>
-      <c r="O43" s="230"/>
+      <c r="D43" s="231"/>
+      <c r="E43" s="231"/>
+      <c r="F43" s="231"/>
+      <c r="G43" s="231"/>
+      <c r="H43" s="231"/>
+      <c r="I43" s="231"/>
+      <c r="J43" s="231"/>
+      <c r="K43" s="231"/>
+      <c r="L43" s="231"/>
+      <c r="M43" s="231"/>
+      <c r="N43" s="231"/>
+      <c r="O43" s="231"/>
       <c r="Q43" s="4"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="230"/>
-      <c r="E44" s="230"/>
-      <c r="F44" s="230"/>
-      <c r="G44" s="230"/>
-      <c r="H44" s="230"/>
-      <c r="I44" s="230"/>
-      <c r="J44" s="230"/>
-      <c r="K44" s="230"/>
-      <c r="L44" s="230"/>
-      <c r="M44" s="230"/>
-      <c r="N44" s="230"/>
-      <c r="O44" s="230"/>
+      <c r="D44" s="231"/>
+      <c r="E44" s="231"/>
+      <c r="F44" s="231"/>
+      <c r="G44" s="231"/>
+      <c r="H44" s="231"/>
+      <c r="I44" s="231"/>
+      <c r="J44" s="231"/>
+      <c r="K44" s="231"/>
+      <c r="L44" s="231"/>
+      <c r="M44" s="231"/>
+      <c r="N44" s="231"/>
+      <c r="O44" s="231"/>
       <c r="Q44" s="4"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="230"/>
-      <c r="E45" s="230"/>
-      <c r="F45" s="230"/>
-      <c r="G45" s="230"/>
-      <c r="H45" s="230"/>
-      <c r="I45" s="230"/>
-      <c r="J45" s="230"/>
-      <c r="K45" s="230"/>
-      <c r="L45" s="230"/>
-      <c r="M45" s="230"/>
-      <c r="N45" s="230"/>
-      <c r="O45" s="230"/>
+      <c r="D45" s="231"/>
+      <c r="E45" s="231"/>
+      <c r="F45" s="231"/>
+      <c r="G45" s="231"/>
+      <c r="H45" s="231"/>
+      <c r="I45" s="231"/>
+      <c r="J45" s="231"/>
+      <c r="K45" s="231"/>
+      <c r="L45" s="231"/>
+      <c r="M45" s="231"/>
+      <c r="N45" s="231"/>
+      <c r="O45" s="231"/>
       <c r="Q45" s="4"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13288,6 +13288,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="D40:O45"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
@@ -13301,13 +13306,8 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>